--- a/doctool/test/auto/scenario35/システム機能設計書_サンプル_S35.xlsx
+++ b/doctool/test/auto/scenario35/システム機能設計書_サンプル_S35.xlsx
@@ -2262,113 +2262,1109 @@
         <t>山田　太郎:a
 aカテゴリの指摘内容サンプル。設計書の記述を確認すること。
 ---
-対応しました。
+対応済みです。
 済</t>
       </text>
     </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:b
+bカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
     <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:b
-bカテゴリの指摘内容サンプル。設計書の記述を確認すること。
----
-対応しました。
-済</t>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:c
 cカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:d
 dカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B9" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:e
 eカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:f
 fカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B11" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:g
 gカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B12" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:h
 hカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
+    <comment ref="B13" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:i
 iカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
+    <comment ref="B14" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:j
 jカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+    <comment ref="B15" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:k
-kカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
+kカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:l
 lカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
+    <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:m
 mカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:n
 nカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
+    <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:o
 oカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B35" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:p
 pカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
+    <comment ref="B21" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:q
 qカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B39" authorId="0" shapeId="0">
+    <comment ref="B22" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:r
 rカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:s
+sカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:t
+tカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:u
+uカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:v
+vカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:w
+wカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:x
+xカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:y
+yカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:z
+zカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:aa
+aaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ab
+abカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ac
+acカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ad
+adカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ae
+aeカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:af
+afカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ag
+agカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ah
+ahカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ai
+aiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:aj
+ajカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ak
+akカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:al
+alカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:am
+amカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:an
+anカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ao
+aoカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ap
+apカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:aq
+aqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ar
+arカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:as
+asカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:at
+atカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:au
+auカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:av
+avカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:aw
+awカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ax
+axカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ay
+ayカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:az
+azカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ba
+baカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bb
+bbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bc
+bcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bd
+bdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:be
+beカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bf
+bfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bg
+bgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bh
+bhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bi
+biカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bj
+bjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bk
+bkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bl
+blカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bm
+bmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bn
+bnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bo
+boカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bp
+bpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bq
+bqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:br
+brカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bs
+bsカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bt
+btカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bu
+buカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bv
+bvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bw
+bwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bx
+bxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:by
+byカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:bz
+bzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ca
+caカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cb
+cbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cc
+ccカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cd
+cdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ce
+ceカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cf
+cfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cg
+cgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ch
+chカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ci
+ciカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cj
+cjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ck
+ckカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cl
+clカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cm
+cmカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cn
+cnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:co
+coカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cp
+cpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cq
+cqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cr
+crカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cs
+csカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ct
+ctカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cu
+cuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cv
+cvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cw
+cwカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cx
+cxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cy
+cyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:cz
+czカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:da
+daカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:db
+dbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dc
+dcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dd
+ddカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:de
+deカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:df
+dfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dg
+dgカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dh
+dhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:di
+diカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dj
+djカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dk
+dkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B120" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dl
+dlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B121" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dm
+dmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dn
+dnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B123" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:do
+doカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B124" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dp
+dpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dq
+dqカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dr
+drカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B127" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ds
+dsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dt
+dtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:du
+duカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B130" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dv
+dvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dw
+dwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dx
+dxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B133" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dy
+dyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B134" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:dz
+dzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ea
+eaカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B136" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eb
+ebカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B137" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ec
+ecカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ed
+edカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ee
+eeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ef
+efカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eg
+egカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eh
+ehカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ei
+eiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ej
+ejカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ek
+ekカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:el
+elカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B147" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:em
+emカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:en
+enカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eo
+eoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ep
+epカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eq
+eqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:er
+erカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B153" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:es
+esカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:et
+etカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:eu
+euカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ev
+evカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B157" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ew
+ewカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ex
+exカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B159" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ey
+eyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B160" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ez
+ezカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fa
+faカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B162" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fb
+fbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fc
+fcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B164" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fd
+fdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B165" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fe
+feカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ff
+ffカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B167" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fg
+fgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B168" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fh
+fhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fi
+fiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B170" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fj
+fjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B171" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fk
+fkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B172" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fl
+flカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fm
+fmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fn
+fnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B175" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fo
+foカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B176" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fp
+fpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B177" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fq
+fqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B178" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fr
+frカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fs
+fsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B180" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ft
+ftカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
   </commentList>
@@ -2383,110 +3379,1112 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>山田　太郎:s
-sカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+        <t>山田　太郎:fu
+fuカテゴリの指摘内容サンプル。設計書の記述を確認すること。
 ---
-対応しました。
+対応済みです。
 済</t>
       </text>
     </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fv
+fvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>山田　太郎:t
-tカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+        <t>山田　太郎:fw
+fwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fx
+fxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fy
+fyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:fz
+fzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ga
+gaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gb
+gbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gc
+gcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gd
+gdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ge
+geカテゴリの指摘内容サンプル。設計書の記述を確認すること。
 ---
-対応しました。
+対応済みです。
 済</t>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:u
-uカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:v
-vカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:w
-wカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:x
-xカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gf
+gfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:y
-yカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:z
-zカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:aa
-aaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:bb
-bbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:cc
-ccカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:dd
-ddカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:ee
-eeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B31" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:ff
-ffカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:gg
 ggカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gh
+ghカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gi
+giカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gj
+gjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gk
+gkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gl
+glカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gm
+gmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gn
+gnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:go
+goカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gp
+gpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gq
+gqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gr
+grカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gs
+gsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gt
+gtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gu
+guカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gv
+gvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gw
+gwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gx
+gxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
     <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gy
+gyカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:gz
+gzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ha
+haカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hb
+hbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hc
+hcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hd
+hdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:he
+heカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hf
+hfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hg
+hgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:hh
 hhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hi
+hiカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hj
+hjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hk
+hkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hl
+hlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hm
+hmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hn
+hnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ho
+hoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hp
+hpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hq
+hqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hr
+hrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hs
+hsカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ht
+htカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hu
+huカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hv
+hvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hw
+hwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hx
+hxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hy
+hyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:hz
+hzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ia
+iaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ib
+ibカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ic
+icカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:id
+idカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ie
+ieカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:if
+ifカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ig
+igカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ih
+ihカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:ii
 iiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ij
+ijカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ik
+ikカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:il
+ilカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:im
+imカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:in
+inカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:io
+ioカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ip
+ipカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iq
+iqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ir
+irカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:is
+isカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:it
+itカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iu
+iuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iv
+ivカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iw
+iwカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ix
+ixカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iy
+iyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:iz
+izカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ja
+jaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jb
+jbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jc
+jcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jd
+jdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:je
+jeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jf
+jfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jg
+jgカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jh
+jhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ji
+jiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jj
+jjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jk
+jkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jl
+jlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jm
+jmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jn
+jnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jo
+joカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jp
+jpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jq
+jqカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jr
+jrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:js
+jsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jt
+jtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ju
+juカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jv
+jvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jw
+jwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jx
+jxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jy
+jyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:jz
+jzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ka
+kaカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kb
+kbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kc
+kcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kd
+kdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ke
+keカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B120" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kf
+kfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B121" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kg
+kgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kh
+khカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B123" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ki
+kiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B124" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kj
+kjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kk
+kkカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kl
+klカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B127" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:km
+kmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kn
+knカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ko
+koカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B130" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kp
+kpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kq
+kqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kr
+krカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B133" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ks
+ksカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B134" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kt
+ktカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ku
+kuカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B136" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kv
+kvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B137" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kw
+kwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kx
+kxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ky
+kyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:kz
+kzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:la
+laカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lb
+lbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lc
+lcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ld
+ldカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:le
+leカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lf
+lfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B147" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lg
+lgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lh
+lhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:li
+liカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lj
+ljカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lk
+lkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ll
+llカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B153" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lm
+lmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ln
+lnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lo
+loカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lp
+lpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B157" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lq
+lqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lr
+lrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B159" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ls
+lsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B160" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lt
+ltカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lu
+luカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B162" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lv
+lvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lw
+lwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B164" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lx
+lxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B165" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ly
+lyカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:lz
+lzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B167" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ma
+maカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B168" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mb
+mbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mc
+mcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B170" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:md
+mdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B171" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:me
+meカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B172" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mf
+mfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mg
+mgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mh
+mhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B175" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mi
+miカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B176" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mj
+mjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B177" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mk
+mkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B178" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ml
+mlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mm
+mmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B180" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mn
+mnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
   </commentList>
@@ -2501,107 +4499,2217 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>山田　太郎:jj
-jjカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+        <t>山田　太郎:mo
+moカテゴリの指摘内容サンプル。設計書の記述を確認すること。
 ---
-対応しました。
+対応済みです。
 済</t>
       </text>
     </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mp
+mpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>山田　太郎:kk
-kkカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+        <t>山田　太郎:mq
+mqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mr
+mrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ms
+msカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mt
+mtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mu
+muカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mv
+mvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mw
+mwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mx
+mxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:my
+myカテゴリの指摘内容サンプル。設計書の記述を確認すること。
 ---
-対応しました。
+対応済みです。
 済</t>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:ll
-llカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
-      <text>
-        <t>山田　太郎:mm
-mmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B13" authorId="0" shapeId="0">
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:mz
+mzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:na
+naカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nb
+nbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nc
+ncカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nd
+ndカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ne
+neカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nf
+nfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ng
+ngカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nh
+nhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ni
+niカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nj
+njカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nk
+nkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nl
+nlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nm
+nmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:nn
 nnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0">
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:no
+noカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:np
+npカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nq
+nqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nr
+nrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ns
+nsカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nt
+ntカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nu
+nuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nv
+nvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nw
+nwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nx
+nxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ny
+nyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:nz
+nzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oa
+oaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ob
+obカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oc
+ocカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:od
+odカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oe
+oeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:of
+ofカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:og
+ogカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oh
+ohカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oi
+oiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oj
+ojカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ok
+okカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ol
+olカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:om
+omカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:on
+onカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:oo
 ooカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:op
+opカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oq
+oqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:or
+orカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:os
+osカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ot
+otカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ou
+ouカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ov
+ovカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ow
+owカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ox
+oxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oy
+oyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:oz
+ozカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pa
+paカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pb
+pbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pc
+pcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pd
+pdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pe
+peカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pf
+pfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pg
+pgカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ph
+phカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pi
+piカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pj
+pjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pk
+pkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pl
+plカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pm
+pmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pn
+pnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:po
+poカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:pp
 ppカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pq
+pqカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pr
+prカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ps
+psカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pt
+ptカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pu
+puカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pv
+pvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pw
+pwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:px
+pxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:py
+pyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:pz
+pzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qa
+qaカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qb
+qbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qc
+qcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qd
+qdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qe
+qeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qf
+qfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qg
+qgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qh
+qhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qi
+qiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qj
+qjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qk
+qkカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ql
+qlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qm
+qmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qn
+qnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qo
+qoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qp
+qpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:qq
 qqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qr
+qrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qs
+qsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qt
+qtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qu
+quカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qv
+qvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qw
+qwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qx
+qxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qy
+qyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B120" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:qz
+qzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B121" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ra
+raカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rb
+rbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B123" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rc
+rcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B124" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rd
+rdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:re
+reカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rf
+rfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B127" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rg
+rgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rh
+rhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ri
+riカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B130" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rj
+rjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rk
+rkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rl
+rlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B133" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rm
+rmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B134" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rn
+rnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ro
+roカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B136" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rp
+rpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B137" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rq
+rqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:rr
 rrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
+    <comment ref="B139" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rs
+rsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rt
+rtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ru
+ruカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rv
+rvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rw
+rwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rx
+rxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ry
+ryカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:rz
+rzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B147" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sa
+saカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sb
+sbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sc
+scカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sd
+sdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:se
+seカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sf
+sfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B153" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sg
+sgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sh
+shカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:si
+siカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sj
+sjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B157" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sk
+skカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sl
+slカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B159" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sm
+smカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B160" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sn
+snカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:so
+soカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B162" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sp
+spカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sq
+sqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B164" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sr
+srカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B165" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:ss
-ssカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+ssカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:st
+stカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B167" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:su
+suカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B168" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sv
+svカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sw
+swカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B170" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sx
+sxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B171" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sy
+syカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B172" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:sz
+szカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ta
+taカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tb
+tbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B175" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tc
+tcカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B176" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:td
+tdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B177" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:te
+teカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B178" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tf
+tfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tg
+tgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>山田　太郎</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:th
+thカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ti
+tiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tj
+tjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tk
+tkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tl
+tlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tm
+tmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tn
+tnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:to
+toカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tp
+tpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B14" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tq
+tqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B15" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tr
+trカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ts
+tsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:tt
 ttカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
+    <comment ref="B18" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tu
+tuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tv
+tvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tw
+twカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tx
+txカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ty
+tyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B23" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:tz
+tzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B24" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ua
+uaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B25" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ub
+ubカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uc
+ucカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
     <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ud
+udカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B28" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ue
+ueカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uf
+ufカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ug
+ugカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B31" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uh
+uhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B32" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ui
+uiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B33" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uj
+ujカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B34" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uk
+ukカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B35" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ul
+ulカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B36" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:um
+umカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B37" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:un
+unカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B38" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uo
+uoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B39" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:up
+upカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B40" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uq
+uqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ur
+urカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B42" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:us
+usカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B43" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ut
+utカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B44" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:uu
 uuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
+    <comment ref="B45" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uv
+uvカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uw
+uwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B47" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ux
+uxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B48" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uy
+uyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B49" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:uz
+uzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B50" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:va
+vaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B51" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vb
+vbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B52" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vc
+vcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B53" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vd
+vdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B54" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ve
+veカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B55" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vf
+vfカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B56" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vg
+vgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vh
+vhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B58" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vi
+viカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B59" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vj
+vjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B60" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vk
+vkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B61" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vl
+vlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vm
+vmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B63" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vn
+vnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B64" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vo
+voカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B65" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vp
+vpカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B66" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vq
+vqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B67" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vr
+vrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B68" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vs
+vsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B69" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vt
+vtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B70" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vu
+vuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B71" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:vv
 vvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0">
+    <comment ref="B72" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vw
+vwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B73" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vx
+vxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B74" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vy
+vyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B75" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:vz
+vzカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B76" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wa
+waカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B77" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wb
+wbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B78" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wc
+wcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wd
+wdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B80" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:we
+weカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B81" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wf
+wfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B82" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wg
+wgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B83" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wh
+whカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B84" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wi
+wiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B85" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wj
+wjカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B86" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wk
+wkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wl
+wlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wm
+wmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B89" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wn
+wnカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B90" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wo
+woカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B91" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wp
+wpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B92" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wq
+wqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B93" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wr
+wrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B94" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ws
+wsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wt
+wtカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B96" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wu
+wuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wv
+wvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B98" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:ww
 wwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wx
+wxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wy
+wyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:wz
+wzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xa
+xaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xb
+xbカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xc
+xcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B105" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xd
+xdカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B106" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xe
+xeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xf
+xfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xg
+xgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xh
+xhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B110" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xi
+xiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B111" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xj
+xjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B112" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xk
+xkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B113" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xl
+xlカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B114" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xm
+xmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B115" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xn
+xnカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xo
+xoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xp
+xpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B118" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xq
+xqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B119" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xr
+xrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B120" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xs
+xsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B121" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xt
+xtカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B122" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xu
+xuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B123" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xv
+xvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B124" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xw
+xwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B125" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:xx
-xxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
-      </text>
-    </comment>
-    <comment ref="B35" authorId="0" shapeId="0">
+xxカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B126" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xy
+xyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B127" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:xz
+xzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B128" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ya
+yaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B129" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yb
+ybカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B130" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yc
+ycカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B131" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yd
+ydカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ye
+yeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B133" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yf
+yfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B134" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yg
+ygカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B135" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yh
+yhカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B136" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yi
+yiカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B137" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yj
+yjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B138" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yk
+ykカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B139" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yl
+ylカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B140" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ym
+ymカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B141" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yn
+ynカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B142" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yo
+yoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B143" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yp
+ypカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B144" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yq
+yqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B145" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yr
+yrカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B146" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ys
+ysカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B147" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yt
+ytカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B148" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yu
+yuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B149" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yv
+yvカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B150" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yw
+ywカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B151" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yx
+yxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B152" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:yy
 yyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
       </text>
     </comment>
-    <comment ref="B37" authorId="0" shapeId="0">
+    <comment ref="B153" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:yz
+yzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B154" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:za
+zaカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B155" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zb
+zbカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B156" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zc
+zcカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B157" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zd
+zdカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B158" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:ze
+zeカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B159" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zf
+zfカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B160" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zg
+zgカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B161" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zh
+zhカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B162" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zi
+ziカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B163" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zj
+zjカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B164" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zk
+zkカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B165" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zl
+zlカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B166" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zm
+zmカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B167" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zn
+znカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B168" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zo
+zoカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B169" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zp
+zpカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B170" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zq
+zqカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B171" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zr
+zrカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B172" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zs
+zsカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B173" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zt
+ztカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B174" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zu
+zuカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B175" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zv
+zvカテゴリの指摘内容サンプル。設計書の記述を確認すること。
+---
+対応済みです。
+済</t>
+      </text>
+    </comment>
+    <comment ref="B176" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zw
+zwカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B177" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zx
+zxカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B178" authorId="0" shapeId="0">
+      <text>
+        <t>山田　太郎:zy
+zyカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
+      </text>
+    </comment>
+    <comment ref="B179" authorId="0" shapeId="0">
       <text>
         <t>山田　太郎:zz
 zzカテゴリの指摘内容サンプル。設計書の記述を確認すること。</t>
@@ -6233,7 +10341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AI39"/>
+  <dimension ref="A1:AI180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="16" min="1" max="16384"/>
@@ -6407,6 +10515,7 @@
       </c>
     </row>
     <row r="6" ht="12" customFormat="1" customHeight="1" s="63">
+      <c r="B6" t="n"/>
       <c r="C6" s="63" t="inlineStr">
         <is>
           <t>1.1. 取引概要</t>
@@ -6685,67 +10794,501 @@
     <row r="15" ht="12" customHeight="1" s="160">
       <c r="B15" t="n"/>
     </row>
-    <row r="16" ht="12" customHeight="1" s="160"/>
+    <row r="16" ht="12" customHeight="1" s="160">
+      <c r="B16" t="n"/>
+    </row>
     <row r="17" ht="12" customHeight="1" s="160">
       <c r="B17" t="n"/>
     </row>
-    <row r="18" ht="12" customHeight="1" s="160"/>
+    <row r="18" ht="12" customHeight="1" s="160">
+      <c r="B18" t="n"/>
+    </row>
     <row r="19" ht="12" customHeight="1" s="160">
       <c r="B19" t="n"/>
     </row>
-    <row r="20" ht="12" customHeight="1" s="160"/>
+    <row r="20" ht="12" customHeight="1" s="160">
+      <c r="B20" t="n"/>
+    </row>
     <row r="21" ht="12" customHeight="1" s="160">
       <c r="B21" t="n"/>
     </row>
-    <row r="22" ht="12" customHeight="1" s="160"/>
+    <row r="22" ht="12" customHeight="1" s="160">
+      <c r="B22" t="n"/>
+    </row>
     <row r="23" ht="12" customHeight="1" s="160">
       <c r="B23" t="n"/>
     </row>
-    <row r="24" ht="12" customHeight="1" s="160"/>
+    <row r="24" ht="12" customHeight="1" s="160">
+      <c r="B24" t="n"/>
+    </row>
     <row r="25" ht="12" customHeight="1" s="160">
       <c r="B25" t="n"/>
     </row>
-    <row r="26" ht="12" customHeight="1" s="160"/>
+    <row r="26" ht="12" customHeight="1" s="160">
+      <c r="B26" t="n"/>
+    </row>
     <row r="27" ht="12" customHeight="1" s="160">
       <c r="B27" t="n"/>
     </row>
-    <row r="28" ht="12" customHeight="1" s="160"/>
+    <row r="28" ht="12" customHeight="1" s="160">
+      <c r="B28" t="n"/>
+    </row>
     <row r="29" ht="12" customHeight="1" s="160">
       <c r="B29" t="n"/>
     </row>
-    <row r="30" ht="12" customHeight="1" s="160"/>
+    <row r="30" ht="12" customHeight="1" s="160">
+      <c r="B30" t="n"/>
+    </row>
     <row r="31" ht="12" customHeight="1" s="160">
       <c r="B31" t="n"/>
     </row>
-    <row r="32" ht="12" customHeight="1" s="160"/>
+    <row r="32" ht="12" customHeight="1" s="160">
+      <c r="B32" t="n"/>
+    </row>
     <row r="33" ht="12" customHeight="1" s="160">
       <c r="B33" t="n"/>
     </row>
-    <row r="34" ht="12" customHeight="1" s="160"/>
+    <row r="34" ht="12" customHeight="1" s="160">
+      <c r="B34" t="n"/>
+    </row>
     <row r="35" ht="12" customHeight="1" s="160">
       <c r="B35" t="n"/>
     </row>
-    <row r="36" ht="12" customHeight="1" s="160"/>
+    <row r="36" ht="12" customHeight="1" s="160">
+      <c r="B36" t="n"/>
+    </row>
     <row r="37" ht="12" customHeight="1" s="160">
       <c r="B37" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1" s="160"/>
+    <row r="38" ht="12" customHeight="1" s="160">
+      <c r="B38" t="n"/>
+    </row>
     <row r="39" ht="12" customHeight="1" s="160">
       <c r="B39" t="n"/>
     </row>
-    <row r="40" ht="12" customHeight="1" s="160"/>
-    <row r="41" ht="12" customHeight="1" s="160"/>
-    <row r="42" ht="12" customHeight="1" s="160"/>
-    <row r="43" ht="12" customHeight="1" s="160"/>
-    <row r="44" ht="12" customHeight="1" s="160"/>
-    <row r="45" ht="12" customHeight="1" s="160"/>
-    <row r="46" ht="12" customHeight="1" s="160"/>
-    <row r="47" ht="12" customHeight="1" s="160"/>
-    <row r="48" ht="12" customHeight="1" s="160"/>
-    <row r="49" ht="12" customHeight="1" s="160"/>
-    <row r="50" ht="12" customHeight="1" s="160"/>
-    <row r="51" ht="12" customHeight="1" s="160"/>
-    <row r="52" ht="12" customHeight="1" s="160"/>
+    <row r="40" ht="12" customHeight="1" s="160">
+      <c r="B40" t="n"/>
+    </row>
+    <row r="41" ht="12" customHeight="1" s="160">
+      <c r="B41" t="n"/>
+    </row>
+    <row r="42" ht="12" customHeight="1" s="160">
+      <c r="B42" t="n"/>
+    </row>
+    <row r="43" ht="12" customHeight="1" s="160">
+      <c r="B43" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1" s="160">
+      <c r="B44" t="n"/>
+    </row>
+    <row r="45" ht="12" customHeight="1" s="160">
+      <c r="B45" t="n"/>
+    </row>
+    <row r="46" ht="12" customHeight="1" s="160">
+      <c r="B46" t="n"/>
+    </row>
+    <row r="47" ht="12" customHeight="1" s="160">
+      <c r="B47" t="n"/>
+    </row>
+    <row r="48" ht="12" customHeight="1" s="160">
+      <c r="B48" t="n"/>
+    </row>
+    <row r="49" ht="12" customHeight="1" s="160">
+      <c r="B49" t="n"/>
+    </row>
+    <row r="50" ht="12" customHeight="1" s="160">
+      <c r="B50" t="n"/>
+    </row>
+    <row r="51" ht="12" customHeight="1" s="160">
+      <c r="B51" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1" s="160">
+      <c r="B52" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" t="n"/>
+    </row>
+    <row r="56">
+      <c r="B56" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" t="n"/>
+    </row>
+    <row r="58">
+      <c r="B58" t="n"/>
+    </row>
+    <row r="59">
+      <c r="B59" t="n"/>
+    </row>
+    <row r="60">
+      <c r="B60" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" t="n"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="n"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="n"/>
+    </row>
+    <row r="65">
+      <c r="B65" t="n"/>
+    </row>
+    <row r="66">
+      <c r="B66" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="n"/>
+    </row>
+    <row r="70">
+      <c r="B70" t="n"/>
+    </row>
+    <row r="71">
+      <c r="B71" t="n"/>
+    </row>
+    <row r="72">
+      <c r="B72" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" t="n"/>
+    </row>
+    <row r="74">
+      <c r="B74" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" t="n"/>
+    </row>
+    <row r="76">
+      <c r="B76" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="23">
     <mergeCell ref="AG2:AI2"/>
@@ -6793,7 +11336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BF179"/>
+  <dimension ref="A1:BF180"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="16" min="1" max="7"/>
@@ -6971,6 +11514,7 @@
       <c r="AM5" s="140" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1" s="160">
+      <c r="B6" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>2.1. 画面レイアウト</t>
@@ -6980,77 +11524,128 @@
     <row r="7" ht="12" customHeight="1" s="160">
       <c r="B7" t="n"/>
     </row>
-    <row r="8" ht="12" customHeight="1" s="160"/>
+    <row r="8" ht="12" customHeight="1" s="160">
+      <c r="B8" t="n"/>
+    </row>
     <row r="9" ht="12" customHeight="1" s="160">
       <c r="B9" t="n"/>
     </row>
-    <row r="10" ht="12" customHeight="1" s="160"/>
+    <row r="10" ht="12" customHeight="1" s="160">
+      <c r="B10" t="n"/>
+    </row>
     <row r="11" ht="12" customHeight="1" s="160">
       <c r="B11" t="n"/>
     </row>
-    <row r="12" ht="12" customHeight="1" s="160"/>
+    <row r="12" ht="12" customHeight="1" s="160">
+      <c r="B12" t="n"/>
+    </row>
     <row r="13" ht="12" customHeight="1" s="160">
       <c r="B13" t="n"/>
     </row>
-    <row r="14" ht="12" customHeight="1" s="160"/>
+    <row r="14" ht="12" customHeight="1" s="160">
+      <c r="B14" t="n"/>
+    </row>
     <row r="15" ht="12" customHeight="1" s="160">
       <c r="B15" t="n"/>
     </row>
-    <row r="16" ht="12" customHeight="1" s="160"/>
+    <row r="16" ht="12" customHeight="1" s="160">
+      <c r="B16" t="n"/>
+    </row>
     <row r="17" ht="12" customHeight="1" s="160">
       <c r="B17" t="n"/>
     </row>
-    <row r="18" ht="12" customHeight="1" s="160"/>
+    <row r="18" ht="12" customHeight="1" s="160">
+      <c r="B18" t="n"/>
+    </row>
     <row r="19" ht="12" customHeight="1" s="160">
       <c r="B19" t="n"/>
     </row>
-    <row r="20" ht="12" customHeight="1" s="160"/>
+    <row r="20" ht="12" customHeight="1" s="160">
+      <c r="B20" t="n"/>
+    </row>
     <row r="21" ht="12" customHeight="1" s="160">
       <c r="B21" t="n"/>
     </row>
-    <row r="22" ht="12" customHeight="1" s="160"/>
+    <row r="22" ht="12" customHeight="1" s="160">
+      <c r="B22" t="n"/>
+    </row>
     <row r="23" ht="12" customHeight="1" s="160">
       <c r="B23" t="n"/>
     </row>
-    <row r="24" ht="12" customHeight="1" s="160"/>
+    <row r="24" ht="12" customHeight="1" s="160">
+      <c r="B24" t="n"/>
+    </row>
     <row r="25" ht="12" customHeight="1" s="160">
       <c r="B25" t="n"/>
     </row>
-    <row r="26" ht="12" customHeight="1" s="160"/>
+    <row r="26" ht="12" customHeight="1" s="160">
+      <c r="B26" t="n"/>
+    </row>
     <row r="27" ht="12" customHeight="1" s="160">
       <c r="B27" t="n"/>
     </row>
-    <row r="28" ht="12" customHeight="1" s="160"/>
+    <row r="28" ht="12" customHeight="1" s="160">
+      <c r="B28" t="n"/>
+    </row>
     <row r="29" ht="12" customHeight="1" s="160">
       <c r="B29" t="n"/>
     </row>
-    <row r="30" ht="12" customHeight="1" s="160"/>
+    <row r="30" ht="12" customHeight="1" s="160">
+      <c r="B30" t="n"/>
+    </row>
     <row r="31" ht="12" customHeight="1" s="160">
       <c r="B31" t="n"/>
     </row>
-    <row r="32" ht="12" customHeight="1" s="160"/>
+    <row r="32" ht="12" customHeight="1" s="160">
+      <c r="B32" t="n"/>
+    </row>
     <row r="33" ht="12" customHeight="1" s="160">
       <c r="B33" t="n"/>
     </row>
-    <row r="34" ht="12" customHeight="1" s="160"/>
+    <row r="34" ht="12" customHeight="1" s="160">
+      <c r="B34" t="n"/>
+    </row>
     <row r="35" ht="12" customHeight="1" s="160">
       <c r="B35" t="n"/>
     </row>
-    <row r="36" ht="12" customHeight="1" s="160"/>
+    <row r="36" ht="12" customHeight="1" s="160">
+      <c r="B36" t="n"/>
+    </row>
     <row r="37" ht="12" customHeight="1" s="160">
       <c r="B37" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1" s="160"/>
-    <row r="39" ht="12" customHeight="1" s="160"/>
-    <row r="40" ht="12" customHeight="1" s="160"/>
-    <row r="41" ht="12" customHeight="1" s="160"/>
-    <row r="42" ht="12" customHeight="1" s="160"/>
-    <row r="43" ht="12" customHeight="1" s="160"/>
-    <row r="44" ht="12" customHeight="1" s="160"/>
-    <row r="45" ht="12" customHeight="1" s="160"/>
-    <row r="46" ht="12" customHeight="1" s="160"/>
-    <row r="47" ht="12" customHeight="1" s="160"/>
+    <row r="38" ht="12" customHeight="1" s="160">
+      <c r="B38" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1" s="160">
+      <c r="B39" t="n"/>
+    </row>
+    <row r="40" ht="12" customHeight="1" s="160">
+      <c r="B40" t="n"/>
+    </row>
+    <row r="41" ht="12" customHeight="1" s="160">
+      <c r="B41" t="n"/>
+    </row>
+    <row r="42" ht="12" customHeight="1" s="160">
+      <c r="B42" t="n"/>
+    </row>
+    <row r="43" ht="12" customHeight="1" s="160">
+      <c r="B43" t="n"/>
+    </row>
+    <row r="44" ht="12" customHeight="1" s="160">
+      <c r="B44" t="n"/>
+    </row>
+    <row r="45" ht="12" customHeight="1" s="160">
+      <c r="B45" t="n"/>
+    </row>
+    <row r="46" ht="12" customHeight="1" s="160">
+      <c r="B46" t="n"/>
+    </row>
+    <row r="47" ht="12" customHeight="1" s="160">
+      <c r="B47" t="n"/>
+    </row>
     <row r="48">
+      <c r="B48" t="n"/>
       <c r="C48" s="26" t="inlineStr">
         <is>
           <t>2.2. 一覧表示</t>
@@ -7088,6 +11683,7 @@
       <c r="AH48" s="103" t="n"/>
     </row>
     <row r="49">
+      <c r="B49" t="n"/>
       <c r="C49" s="29" t="n"/>
       <c r="D49" s="103" t="n"/>
       <c r="E49" s="103" t="n"/>
@@ -7121,6 +11717,7 @@
       <c r="AH49" s="103" t="n"/>
     </row>
     <row r="50">
+      <c r="B50" t="n"/>
       <c r="D50" s="97" t="inlineStr">
         <is>
           <t>No.</t>
@@ -7174,6 +11771,7 @@
       <c r="AH50" s="103" t="n"/>
     </row>
     <row r="51" ht="11.25" customHeight="1" s="160">
+      <c r="B51" t="n"/>
       <c r="D51" s="121" t="n">
         <v>1</v>
       </c>
@@ -7221,6 +11819,7 @@
       <c r="AM51" s="29" t="n"/>
     </row>
     <row r="52" ht="11.25" customHeight="1" s="160">
+      <c r="B52" t="n"/>
       <c r="D52" s="123" t="n"/>
       <c r="E52" s="114" t="n"/>
       <c r="F52" s="122" t="n"/>
@@ -7250,10 +11849,12 @@
       <c r="AM52" s="29" t="n"/>
     </row>
     <row r="53" ht="11.25" customHeight="1" s="160">
+      <c r="B53" t="n"/>
       <c r="L53" s="1" t="n"/>
       <c r="O53" s="122" t="n"/>
     </row>
     <row r="54">
+      <c r="B54" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>2.3. 画面項目定義</t>
@@ -7278,6 +11879,7 @@
       <c r="BA54" s="64" t="n"/>
     </row>
     <row r="55" customFormat="1" s="63">
+      <c r="B55" t="n"/>
       <c r="AJ55" s="92" t="n"/>
       <c r="AK55" s="92" t="n"/>
       <c r="AL55" s="92" t="n"/>
@@ -7297,6 +11899,7 @@
       <c r="AZ55" s="92" t="n"/>
     </row>
     <row r="56" customFormat="1" s="63">
+      <c r="B56" t="n"/>
       <c r="D56" s="239" t="inlineStr">
         <is>
           <t>No.</t>
@@ -7352,6 +11955,7 @@
       <c r="AN56" s="92" t="n"/>
     </row>
     <row r="57" ht="11.25" customFormat="1" customHeight="1" s="63">
+      <c r="B57" t="n"/>
       <c r="D57" s="462" t="n"/>
       <c r="E57" s="239" t="inlineStr">
         <is>
@@ -7419,6 +12023,7 @@
       <c r="AT57" s="92" t="n"/>
     </row>
     <row r="58" customFormat="1" s="63">
+      <c r="B58" t="n"/>
       <c r="D58" s="465" t="n"/>
       <c r="E58" s="435" t="n"/>
       <c r="F58" s="436" t="n"/>
@@ -7469,6 +12074,7 @@
       <c r="AT58" s="92" t="n"/>
     </row>
     <row r="59" customFormat="1" s="63">
+      <c r="B59" t="n"/>
       <c r="D59" s="467" t="inlineStr">
         <is>
           <t>領域名：プロジェクト情報入力</t>
@@ -7522,6 +12128,7 @@
       <c r="AT59" s="92" t="n"/>
     </row>
     <row r="60" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B60" t="n"/>
       <c r="D60" s="106" t="n">
         <v>1</v>
       </c>
@@ -7593,6 +12200,7 @@
       <c r="AP60" s="366" t="n"/>
     </row>
     <row r="61" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B61" t="n"/>
       <c r="D61" s="106" t="n">
         <v>2</v>
       </c>
@@ -7664,6 +12272,7 @@
       <c r="AP61" s="366" t="n"/>
     </row>
     <row r="62" ht="11.25" customFormat="1" customHeight="1" s="63">
+      <c r="B62" t="n"/>
       <c r="D62" s="106" t="n">
         <v>3</v>
       </c>
@@ -7743,6 +12352,7 @@
       <c r="AT62" s="92" t="n"/>
     </row>
     <row r="63" ht="95.25" customFormat="1" customHeight="1" s="63">
+      <c r="B63" t="n"/>
       <c r="D63" s="106" t="n">
         <v>4</v>
       </c>
@@ -7827,6 +12437,7 @@
       <c r="AT63" s="92" t="n"/>
     </row>
     <row r="64" ht="95.25" customFormat="1" customHeight="1" s="63">
+      <c r="B64" t="n"/>
       <c r="D64" s="106" t="n">
         <v>5</v>
       </c>
@@ -7911,6 +12522,7 @@
       <c r="AT64" s="92" t="n"/>
     </row>
     <row r="65" ht="11.25" customHeight="1" s="160">
+      <c r="B65" t="n"/>
       <c r="D65" s="106" t="n">
         <v>6</v>
       </c>
@@ -7982,6 +12594,7 @@
       <c r="AP65" s="366" t="n"/>
     </row>
     <row r="66" ht="24.75" customFormat="1" customHeight="1" s="64">
+      <c r="B66" t="n"/>
       <c r="D66" s="106" t="n">
         <v>7</v>
       </c>
@@ -8053,6 +12666,7 @@
       <c r="AP66" s="366" t="n"/>
     </row>
     <row r="67" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B67" t="n"/>
       <c r="D67" s="106" t="n">
         <v>8</v>
       </c>
@@ -8125,6 +12739,7 @@
       <c r="AV67" s="75" t="n"/>
     </row>
     <row r="68" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B68" t="n"/>
       <c r="D68" s="106" t="n">
         <v>9</v>
       </c>
@@ -8198,6 +12813,7 @@
       <c r="AS68" s="92" t="n"/>
     </row>
     <row r="69" ht="22.5" customFormat="1" customHeight="1" s="63">
+      <c r="B69" t="n"/>
       <c r="D69" s="106" t="n">
         <v>10</v>
       </c>
@@ -8276,6 +12892,7 @@
       <c r="AR69" s="92" t="n"/>
     </row>
     <row r="70" ht="22.5" customFormat="1" customHeight="1" s="64">
+      <c r="B70" t="n"/>
       <c r="D70" s="106" t="n">
         <v>11</v>
       </c>
@@ -8348,6 +12965,7 @@
       <c r="AP70" s="366" t="n"/>
     </row>
     <row r="71">
+      <c r="B71" t="n"/>
       <c r="D71" s="106" t="n">
         <v>12</v>
       </c>
@@ -8418,8 +13036,11 @@
       <c r="AO71" s="365" t="n"/>
       <c r="AP71" s="366" t="n"/>
     </row>
-    <row r="72" ht="11.25" customHeight="1" s="160"/>
+    <row r="72" ht="11.25" customHeight="1" s="160">
+      <c r="B72" t="n"/>
+    </row>
     <row r="73">
+      <c r="B73" t="n"/>
       <c r="D73" s="64" t="n"/>
       <c r="E73" s="96" t="n"/>
       <c r="F73" s="96" t="n"/>
@@ -8456,6 +13077,7 @@
       <c r="AK73" s="96" t="n"/>
     </row>
     <row r="74">
+      <c r="B74" t="n"/>
       <c r="C74" s="16" t="inlineStr">
         <is>
           <t>2.4. 入出力一覧</t>
@@ -8497,10 +13119,12 @@
       <c r="AK74" s="96" t="n"/>
     </row>
     <row r="75" ht="11.25" customHeight="1" s="160">
+      <c r="B75" t="n"/>
       <c r="AI75" s="96" t="n"/>
       <c r="AJ75" s="96" t="n"/>
     </row>
     <row r="76">
+      <c r="B76" t="n"/>
       <c r="D76" s="469" t="inlineStr">
         <is>
           <t>No.</t>
@@ -8558,6 +13182,7 @@
       <c r="AH76" s="428" t="n"/>
     </row>
     <row r="77">
+      <c r="B77" t="n"/>
       <c r="D77" s="465" t="n"/>
       <c r="E77" s="435" t="n"/>
       <c r="F77" s="436" t="n"/>
@@ -8611,6 +13236,7 @@
       <c r="AH77" s="437" t="n"/>
     </row>
     <row r="78">
+      <c r="B78" t="n"/>
       <c r="D78" s="111" t="n">
         <v>1</v>
       </c>
@@ -8682,6 +13308,7 @@
       <c r="AH78" s="366" t="n"/>
     </row>
     <row r="79">
+      <c r="B79" t="n"/>
       <c r="D79" s="101" t="n"/>
       <c r="E79" s="104" t="n"/>
       <c r="F79" s="104" t="n"/>
@@ -8715,6 +13342,7 @@
       <c r="AH79" s="318" t="n"/>
     </row>
     <row r="80">
+      <c r="B80" t="n"/>
       <c r="D80" s="64" t="n"/>
       <c r="E80" s="96" t="n"/>
       <c r="F80" s="96" t="n"/>
@@ -8748,14 +13376,18 @@
       <c r="AJ80" s="96" t="n"/>
     </row>
     <row r="81">
+      <c r="B81" t="n"/>
       <c r="C81" s="16" t="inlineStr">
         <is>
           <t>2.5. 画面イベント一覧</t>
         </is>
       </c>
     </row>
-    <row r="82"/>
+    <row r="82">
+      <c r="B82" t="n"/>
+    </row>
     <row r="83" ht="11.25" customHeight="1" s="160">
+      <c r="B83" t="n"/>
       <c r="C83" s="75" t="n"/>
       <c r="D83" s="113" t="inlineStr">
         <is>
@@ -8814,6 +13446,7 @@
       <c r="AH83" s="459" t="n"/>
     </row>
     <row r="84" ht="27" customHeight="1" s="160">
+      <c r="B84" t="n"/>
       <c r="D84" s="106" t="n">
         <v>1</v>
       </c>
@@ -8869,6 +13502,7 @@
       <c r="AH84" s="461" t="n"/>
     </row>
     <row r="85" ht="27" customHeight="1" s="160">
+      <c r="B85" t="n"/>
       <c r="D85" s="139" t="n">
         <v>2</v>
       </c>
@@ -8924,6 +13558,7 @@
       <c r="AH85" s="461" t="n"/>
     </row>
     <row r="86" ht="27" customHeight="1" s="160">
+      <c r="B86" t="n"/>
       <c r="D86" s="106" t="n">
         <v>3</v>
       </c>
@@ -8979,6 +13614,7 @@
       <c r="AH86" s="461" t="n"/>
     </row>
     <row r="87" ht="27" customHeight="1" s="160">
+      <c r="B87" t="n"/>
       <c r="D87" s="106" t="n">
         <v>4</v>
       </c>
@@ -9034,6 +13670,7 @@
       <c r="AH87" s="461" t="n"/>
     </row>
     <row r="88">
+      <c r="B88" t="n"/>
       <c r="D88" s="95" t="n"/>
       <c r="E88" s="104" t="n"/>
       <c r="F88" s="104" t="n"/>
@@ -9067,11 +13704,13 @@
       <c r="AH88" s="103" t="n"/>
     </row>
     <row r="89">
+      <c r="B89" t="n"/>
       <c r="AE89" s="104" t="n"/>
       <c r="AF89" s="104" t="n"/>
       <c r="AG89" s="104" t="n"/>
     </row>
     <row r="90">
+      <c r="B90" t="n"/>
       <c r="C90" s="16" t="inlineStr">
         <is>
           <t>2.6. 画面イベント詳細</t>
@@ -9083,6 +13722,7 @@
       <c r="AG90" s="104" t="n"/>
     </row>
     <row r="91" ht="11.25" customHeight="1" s="160">
+      <c r="B91" t="n"/>
       <c r="D91" s="26" t="inlineStr">
         <is>
           <t>2.6.1.初期表示イベント</t>
@@ -9091,10 +13731,12 @@
       <c r="E91" s="29" t="n"/>
     </row>
     <row r="92" ht="11.25" customHeight="1" s="160">
+      <c r="B92" t="n"/>
       <c r="D92" s="29" t="n"/>
       <c r="E92" s="29" t="n"/>
     </row>
     <row r="93" ht="11.25" customHeight="1" s="160">
+      <c r="B93" t="n"/>
       <c r="D93" s="29" t="n"/>
       <c r="E93" s="29" t="inlineStr">
         <is>
@@ -9103,11 +13745,13 @@
       </c>
     </row>
     <row r="94">
+      <c r="B94" t="n"/>
       <c r="D94" s="29" t="n"/>
       <c r="E94" s="29" t="n"/>
       <c r="F94" s="29" t="n"/>
     </row>
     <row r="95" ht="11.25" customHeight="1" s="160">
+      <c r="B95" t="n"/>
       <c r="D95" s="29" t="n"/>
       <c r="E95" s="29" t="n"/>
       <c r="F95" s="16" t="inlineStr">
@@ -9117,6 +13761,7 @@
       </c>
     </row>
     <row r="96">
+      <c r="B96" t="n"/>
       <c r="G96" s="117" t="n"/>
       <c r="H96" s="117" t="n"/>
       <c r="I96" s="117" t="n"/>
@@ -9149,10 +13794,12 @@
       <c r="AJ96" s="96" t="n"/>
     </row>
     <row r="97" ht="11.25" customHeight="1" s="160">
+      <c r="B97" t="n"/>
       <c r="D97" s="29" t="n"/>
       <c r="E97" s="29" t="n"/>
     </row>
     <row r="98">
+      <c r="B98" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>(2) DBアクセス（検索処理）</t>
@@ -9160,14 +13807,18 @@
       </c>
     </row>
     <row r="99">
+      <c r="B99" t="n"/>
       <c r="F99" t="inlineStr">
         <is>
           <t>(a) 組織検索条件</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
+    <row r="100">
+      <c r="B100" t="n"/>
+    </row>
     <row r="101">
+      <c r="B101" t="n"/>
       <c r="G101" s="466" t="inlineStr">
         <is>
           <t>取得テーブル名</t>
@@ -9198,6 +13849,7 @@
       <c r="Z101" s="366" t="n"/>
     </row>
     <row r="102" ht="11.25" customHeight="1" s="160">
+      <c r="B102" t="n"/>
       <c r="G102" s="480" t="inlineStr">
         <is>
           <t>組織</t>
@@ -9230,6 +13882,7 @@
       <c r="AH102" s="76" t="n"/>
     </row>
     <row r="103">
+      <c r="B103" t="n"/>
       <c r="G103" s="432" t="n"/>
       <c r="P103" s="433" t="n"/>
       <c r="Q103" s="52" t="inlineStr">
@@ -9264,6 +13917,7 @@
       <c r="AY103" s="77" t="n"/>
     </row>
     <row r="104">
+      <c r="B104" t="n"/>
       <c r="G104" s="481" t="inlineStr">
         <is>
           <t>検索条件</t>
@@ -9313,6 +13967,7 @@
       <c r="BF104" s="77" t="n"/>
     </row>
     <row r="105">
+      <c r="B105" t="n"/>
       <c r="G105" s="78" t="n"/>
       <c r="H105" s="79" t="n"/>
       <c r="I105" s="79" t="n"/>
@@ -9358,6 +14013,7 @@
       <c r="BF105" s="77" t="n"/>
     </row>
     <row r="106">
+      <c r="B106" t="n"/>
       <c r="G106" s="81" t="n"/>
       <c r="H106" s="132" t="inlineStr">
         <is>
@@ -9415,6 +14071,7 @@
       <c r="BF106" s="77" t="n"/>
     </row>
     <row r="107">
+      <c r="B107" t="n"/>
       <c r="G107" s="86" t="n"/>
       <c r="H107" s="87" t="n"/>
       <c r="I107" s="87" t="n"/>
@@ -9460,6 +14117,7 @@
       <c r="BF107" s="77" t="n"/>
     </row>
     <row r="108">
+      <c r="B108" t="n"/>
       <c r="G108" s="82" t="n"/>
       <c r="H108" s="82" t="n"/>
       <c r="I108" s="82" t="n"/>
@@ -9505,6 +14163,7 @@
       <c r="BF108" s="77" t="n"/>
     </row>
     <row r="109">
+      <c r="B109" t="n"/>
       <c r="AI109" s="77" t="n"/>
       <c r="AJ109" s="77" t="n"/>
       <c r="AK109" s="77" t="n"/>
@@ -9530,6 +14189,7 @@
       <c r="BE109" s="77" t="n"/>
     </row>
     <row r="110">
+      <c r="B110" t="n"/>
       <c r="E110" s="16" t="inlineStr">
         <is>
           <t>(3)　表示処理</t>
@@ -9560,6 +14220,7 @@
       <c r="BF110" s="77" t="n"/>
     </row>
     <row r="111">
+      <c r="B111" t="n"/>
       <c r="AJ111" s="77" t="n"/>
       <c r="AK111" s="77" t="n"/>
       <c r="AL111" s="77" t="n"/>
@@ -9585,6 +14246,7 @@
       <c r="BF111" s="77" t="n"/>
     </row>
     <row r="112">
+      <c r="B112" t="n"/>
       <c r="E112" s="92" t="n"/>
       <c r="F112" s="159" t="inlineStr">
         <is>
@@ -9616,6 +14278,7 @@
       <c r="BF112" s="77" t="n"/>
     </row>
     <row r="113">
+      <c r="B113" t="n"/>
       <c r="E113" s="92" t="n"/>
       <c r="F113" s="93" t="n"/>
       <c r="G113" s="159" t="inlineStr">
@@ -9648,6 +14311,7 @@
       <c r="BF113" s="77" t="n"/>
     </row>
     <row r="114" s="160">
+      <c r="B114" t="n"/>
       <c r="E114" s="159" t="n"/>
       <c r="G114" s="159" t="inlineStr">
         <is>
@@ -9679,6 +14343,7 @@
       <c r="BF114" s="143" t="n"/>
     </row>
     <row r="115">
+      <c r="B115" t="n"/>
       <c r="E115" s="92" t="n"/>
       <c r="F115" s="93" t="n"/>
       <c r="G115" s="159" t="n"/>
@@ -9707,6 +14372,7 @@
       <c r="BF115" s="77" t="n"/>
     </row>
     <row r="116">
+      <c r="B116" t="n"/>
       <c r="E116" s="92" t="n"/>
       <c r="AJ116" s="77" t="n"/>
       <c r="AK116" s="77" t="n"/>
@@ -9733,6 +14399,7 @@
       <c r="BF116" s="77" t="n"/>
     </row>
     <row r="117" ht="11.25" customHeight="1" s="160">
+      <c r="B117" t="n"/>
       <c r="D117" s="26" t="inlineStr">
         <is>
           <t>2.6.2.部門リスト取得イベント</t>
@@ -9741,10 +14408,12 @@
       <c r="E117" s="29" t="n"/>
     </row>
     <row r="118" ht="11.25" customHeight="1" s="160">
+      <c r="B118" t="n"/>
       <c r="D118" s="29" t="n"/>
       <c r="E118" s="29" t="n"/>
     </row>
     <row r="119" ht="11.25" customHeight="1" s="160">
+      <c r="B119" t="n"/>
       <c r="D119" s="29" t="n"/>
       <c r="E119" s="29" t="inlineStr">
         <is>
@@ -9753,11 +14422,13 @@
       </c>
     </row>
     <row r="120">
+      <c r="B120" t="n"/>
       <c r="D120" s="29" t="n"/>
       <c r="E120" s="29" t="n"/>
       <c r="F120" s="29" t="n"/>
     </row>
     <row r="121" ht="11.25" customHeight="1" s="160">
+      <c r="B121" t="n"/>
       <c r="D121" s="29" t="n"/>
       <c r="E121" s="29" t="n"/>
       <c r="F121" s="16" t="inlineStr">
@@ -9767,6 +14438,7 @@
       </c>
     </row>
     <row r="122">
+      <c r="B122" t="n"/>
       <c r="G122" s="117" t="n"/>
       <c r="H122" s="117" t="n"/>
       <c r="I122" s="117" t="n"/>
@@ -9799,10 +14471,12 @@
       <c r="AJ122" s="96" t="n"/>
     </row>
     <row r="123" ht="11.25" customHeight="1" s="160">
+      <c r="B123" t="n"/>
       <c r="D123" s="29" t="n"/>
       <c r="E123" s="29" t="n"/>
     </row>
     <row r="124">
+      <c r="B124" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
           <t>(2) DBアクセス（検索処理）</t>
@@ -9810,14 +14484,18 @@
       </c>
     </row>
     <row r="125">
+      <c r="B125" t="n"/>
       <c r="F125" t="inlineStr">
         <is>
           <t>(a) 組織検索条件</t>
         </is>
       </c>
     </row>
-    <row r="126"/>
+    <row r="126">
+      <c r="B126" t="n"/>
+    </row>
     <row r="127">
+      <c r="B127" t="n"/>
       <c r="G127" s="466" t="inlineStr">
         <is>
           <t>取得テーブル名</t>
@@ -9848,6 +14526,7 @@
       <c r="Z127" s="366" t="n"/>
     </row>
     <row r="128" ht="11.25" customHeight="1" s="160">
+      <c r="B128" t="n"/>
       <c r="G128" s="480" t="inlineStr">
         <is>
           <t>組織</t>
@@ -9880,6 +14559,7 @@
       <c r="AH128" s="76" t="n"/>
     </row>
     <row r="129">
+      <c r="B129" t="n"/>
       <c r="G129" s="432" t="n"/>
       <c r="P129" s="433" t="n"/>
       <c r="Q129" s="52" t="inlineStr">
@@ -9914,6 +14594,7 @@
       <c r="AY129" s="77" t="n"/>
     </row>
     <row r="130">
+      <c r="B130" t="n"/>
       <c r="G130" s="481" t="inlineStr">
         <is>
           <t>検索条件</t>
@@ -9963,6 +14644,7 @@
       <c r="BF130" s="77" t="n"/>
     </row>
     <row r="131">
+      <c r="B131" t="n"/>
       <c r="G131" s="78" t="n"/>
       <c r="H131" s="79" t="n"/>
       <c r="I131" s="79" t="n"/>
@@ -10008,6 +14690,7 @@
       <c r="BF131" s="77" t="n"/>
     </row>
     <row r="132">
+      <c r="B132" t="n"/>
       <c r="G132" s="81" t="n"/>
       <c r="H132" s="132" t="inlineStr">
         <is>
@@ -10065,6 +14748,7 @@
       <c r="BF132" s="77" t="n"/>
     </row>
     <row r="133">
+      <c r="B133" t="n"/>
       <c r="G133" s="86" t="n"/>
       <c r="H133" s="87" t="n"/>
       <c r="I133" s="87" t="n"/>
@@ -10110,6 +14794,7 @@
       <c r="BF133" s="77" t="n"/>
     </row>
     <row r="134">
+      <c r="B134" t="n"/>
       <c r="G134" s="82" t="n"/>
       <c r="H134" s="82" t="n"/>
       <c r="I134" s="82" t="n"/>
@@ -10155,6 +14840,7 @@
       <c r="BF134" s="77" t="n"/>
     </row>
     <row r="135">
+      <c r="B135" t="n"/>
       <c r="AI135" s="77" t="n"/>
       <c r="AJ135" s="77" t="n"/>
       <c r="AK135" s="77" t="n"/>
@@ -10180,6 +14866,7 @@
       <c r="BE135" s="77" t="n"/>
     </row>
     <row r="136">
+      <c r="B136" t="n"/>
       <c r="E136" s="16" t="inlineStr">
         <is>
           <t>(3)　表示処理</t>
@@ -10210,6 +14897,7 @@
       <c r="BF136" s="77" t="n"/>
     </row>
     <row r="137">
+      <c r="B137" t="n"/>
       <c r="AJ137" s="77" t="n"/>
       <c r="AK137" s="77" t="n"/>
       <c r="AL137" s="77" t="n"/>
@@ -10235,6 +14923,7 @@
       <c r="BF137" s="77" t="n"/>
     </row>
     <row r="138">
+      <c r="B138" t="n"/>
       <c r="E138" s="92" t="n"/>
       <c r="F138" s="159" t="inlineStr">
         <is>
@@ -10266,6 +14955,7 @@
       <c r="BF138" s="77" t="n"/>
     </row>
     <row r="139">
+      <c r="B139" t="n"/>
       <c r="E139" s="92" t="n"/>
       <c r="F139" s="93" t="n"/>
       <c r="G139" s="159" t="inlineStr">
@@ -10298,6 +14988,7 @@
       <c r="BF139" s="77" t="n"/>
     </row>
     <row r="140" s="160">
+      <c r="B140" t="n"/>
       <c r="E140" s="159" t="n"/>
       <c r="G140" s="159" t="inlineStr">
         <is>
@@ -10329,6 +15020,7 @@
       <c r="BF140" s="143" t="n"/>
     </row>
     <row r="141">
+      <c r="B141" t="n"/>
       <c r="E141" s="92" t="n"/>
       <c r="AJ141" s="77" t="n"/>
       <c r="AK141" s="77" t="n"/>
@@ -10355,6 +15047,7 @@
       <c r="BF141" s="77" t="n"/>
     </row>
     <row r="142" ht="11.25" customHeight="1" s="160">
+      <c r="B142" t="n"/>
       <c r="D142" s="26" t="inlineStr">
         <is>
           <t>2.6.3.顧客検索イベント</t>
@@ -10363,10 +15056,12 @@
       <c r="E142" s="29" t="n"/>
     </row>
     <row r="143" ht="11.25" customHeight="1" s="160">
+      <c r="B143" t="n"/>
       <c r="D143" s="29" t="n"/>
       <c r="E143" s="29" t="n"/>
     </row>
     <row r="144" ht="11.25" customHeight="1" s="160">
+      <c r="B144" t="n"/>
       <c r="D144" s="29" t="n"/>
       <c r="E144" s="26" t="inlineStr">
         <is>
@@ -10375,11 +15070,13 @@
       </c>
     </row>
     <row r="145">
+      <c r="B145" t="n"/>
       <c r="D145" s="29" t="n"/>
       <c r="E145" s="29" t="n"/>
       <c r="F145" s="29" t="n"/>
     </row>
     <row r="146" ht="11.25" customHeight="1" s="160">
+      <c r="B146" t="n"/>
       <c r="D146" s="29" t="n"/>
       <c r="E146" s="29" t="n"/>
       <c r="F146" s="16" t="inlineStr">
@@ -10389,6 +15086,7 @@
       </c>
     </row>
     <row r="147">
+      <c r="B147" t="n"/>
       <c r="G147" s="117" t="n"/>
       <c r="H147" s="117" t="n"/>
       <c r="I147" s="117" t="n"/>
@@ -10421,10 +15119,12 @@
       <c r="AJ147" s="96" t="n"/>
     </row>
     <row r="148" ht="11.25" customHeight="1" s="160">
+      <c r="B148" t="n"/>
       <c r="D148" s="29" t="n"/>
       <c r="E148" s="29" t="n"/>
     </row>
     <row r="149">
+      <c r="B149" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>(2)　表示処理</t>
@@ -10455,6 +15155,7 @@
       <c r="BF149" s="77" t="n"/>
     </row>
     <row r="150">
+      <c r="B150" t="n"/>
       <c r="AJ150" s="77" t="n"/>
       <c r="AK150" s="77" t="n"/>
       <c r="AL150" s="77" t="n"/>
@@ -10480,6 +15181,7 @@
       <c r="BF150" s="77" t="n"/>
     </row>
     <row r="151">
+      <c r="B151" t="n"/>
       <c r="E151" s="92" t="n"/>
       <c r="F151" s="159" t="inlineStr">
         <is>
@@ -10511,6 +15213,7 @@
       <c r="BF151" s="77" t="n"/>
     </row>
     <row r="152">
+      <c r="B152" t="n"/>
       <c r="E152" s="92" t="n"/>
       <c r="F152" s="93" t="n"/>
       <c r="G152" s="159" t="n"/>
@@ -10539,6 +15242,7 @@
       <c r="BF152" s="77" t="n"/>
     </row>
     <row r="153">
+      <c r="B153" t="n"/>
       <c r="E153" s="92" t="n"/>
       <c r="AJ153" s="77" t="n"/>
       <c r="AK153" s="77" t="n"/>
@@ -10565,6 +15269,7 @@
       <c r="BF153" s="77" t="n"/>
     </row>
     <row r="154">
+      <c r="B154" t="n"/>
       <c r="D154" s="26" t="inlineStr">
         <is>
           <t>2.6.5. 確認イベント</t>
@@ -10596,6 +15301,7 @@
       <c r="BF154" s="77" t="n"/>
     </row>
     <row r="155">
+      <c r="B155" t="n"/>
       <c r="E155" s="29" t="inlineStr">
         <is>
           <t>(1) バリデーション処理</t>
@@ -10627,6 +15333,7 @@
       <c r="BF155" s="77" t="n"/>
     </row>
     <row r="156">
+      <c r="B156" t="n"/>
       <c r="E156" s="29" t="n"/>
       <c r="F156" s="29" t="n"/>
       <c r="AJ156" s="77" t="n"/>
@@ -10654,6 +15361,7 @@
       <c r="BF156" s="77" t="n"/>
     </row>
     <row r="157" ht="41.25" customHeight="1" s="160">
+      <c r="B157" t="n"/>
       <c r="E157" s="29" t="n"/>
       <c r="F157" s="115" t="inlineStr">
         <is>
@@ -10733,6 +15441,7 @@
       <c r="BE157" s="77" t="n"/>
     </row>
     <row r="158" ht="47.25" customHeight="1" s="160">
+      <c r="B158" t="n"/>
       <c r="E158" s="29" t="n"/>
       <c r="F158" s="116" t="n">
         <v>1</v>
@@ -10809,6 +15518,7 @@
       <c r="BE158" s="77" t="n"/>
     </row>
     <row r="159" ht="62.25" customHeight="1" s="160">
+      <c r="B159" t="n"/>
       <c r="E159" s="29" t="n"/>
       <c r="F159" s="116" t="n">
         <v>2</v>
@@ -10884,6 +15594,7 @@
       <c r="BE159" s="77" t="n"/>
     </row>
     <row r="160">
+      <c r="B160" t="n"/>
       <c r="E160" s="29" t="n"/>
       <c r="AI160" s="77" t="n"/>
       <c r="AJ160" s="77" t="n"/>
@@ -10910,6 +15621,7 @@
       <c r="BE160" s="77" t="n"/>
     </row>
     <row r="161">
+      <c r="B161" t="n"/>
       <c r="E161" s="29" t="n"/>
       <c r="F161" t="inlineStr">
         <is>
@@ -10918,10 +15630,12 @@
       </c>
     </row>
     <row r="162">
+      <c r="B162" t="n"/>
       <c r="E162" s="29" t="n"/>
       <c r="F162" s="29" t="n"/>
     </row>
     <row r="163" s="160">
+      <c r="B163" t="n"/>
       <c r="E163" t="inlineStr">
         <is>
           <t>(2) DBアクセス（検索処理）</t>
@@ -10929,6 +15643,7 @@
       </c>
     </row>
     <row r="164" s="160">
+      <c r="B164" t="n"/>
       <c r="F164" t="inlineStr">
         <is>
           <t>(a) 組織検索条件</t>
@@ -10936,6 +15651,7 @@
       </c>
     </row>
     <row r="165" s="160">
+      <c r="B165" t="n"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>Formの事業部、部門には登録画面で選択された組織の組織IDが設定されている。</t>
@@ -10943,14 +15659,18 @@
       </c>
     </row>
     <row r="166" s="160">
+      <c r="B166" t="n"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>画面には組織IDに対する組織名を表示する必要があるので、下記クエリにより組織名を取得する。</t>
         </is>
       </c>
     </row>
-    <row r="167" s="160"/>
+    <row r="167" s="160">
+      <c r="B167" t="n"/>
+    </row>
     <row r="168" s="160">
+      <c r="B168" t="n"/>
       <c r="G168" s="489" t="inlineStr">
         <is>
           <t>取得テーブル名</t>
@@ -10981,6 +15701,7 @@
       <c r="Z168" s="366" t="n"/>
     </row>
     <row r="169" ht="11.25" customHeight="1" s="160">
+      <c r="B169" t="n"/>
       <c r="G169" s="480" t="inlineStr">
         <is>
           <t>組織</t>
@@ -11013,6 +15734,7 @@
       <c r="AH169" s="144" t="n"/>
     </row>
     <row r="170" s="160">
+      <c r="B170" t="n"/>
       <c r="G170" s="490" t="inlineStr">
         <is>
           <t>検索条件</t>
@@ -11062,6 +15784,7 @@
       <c r="BF170" s="143" t="n"/>
     </row>
     <row r="171" s="160">
+      <c r="B171" t="n"/>
       <c r="G171" s="145" t="n"/>
       <c r="H171" s="146" t="n"/>
       <c r="I171" s="146" t="n"/>
@@ -11107,6 +15830,7 @@
       <c r="BF171" s="143" t="n"/>
     </row>
     <row r="172" s="160">
+      <c r="B172" t="n"/>
       <c r="G172" s="148" t="n"/>
       <c r="H172" s="132" t="inlineStr">
         <is>
@@ -11164,6 +15888,7 @@
       <c r="BF172" s="143" t="n"/>
     </row>
     <row r="173" s="160">
+      <c r="B173" t="n"/>
       <c r="G173" s="152" t="n"/>
       <c r="H173" s="153" t="n"/>
       <c r="I173" s="153" t="n"/>
@@ -11209,6 +15934,7 @@
       <c r="BF173" s="143" t="n"/>
     </row>
     <row r="174" s="160">
+      <c r="B174" t="n"/>
       <c r="G174" s="132" t="n"/>
       <c r="H174" s="132" t="n"/>
       <c r="I174" s="132" t="n"/>
@@ -11254,6 +15980,7 @@
       <c r="BF174" s="143" t="n"/>
     </row>
     <row r="175" s="160">
+      <c r="B175" t="n"/>
       <c r="F175" t="inlineStr">
         <is>
           <t>(b)Formに設定された顧客IDをパラメータとして、顧客管理システム．顧客詳細取得APIを実行し顧客名を取得する。</t>
@@ -11304,14 +16031,17 @@
       <c r="BF175" s="143" t="n"/>
     </row>
     <row r="176" s="160">
+      <c r="B176" t="n"/>
       <c r="E176" s="26" t="n"/>
       <c r="F176" s="26" t="n"/>
     </row>
     <row r="177">
+      <c r="B177" t="n"/>
       <c r="E177" s="29" t="n"/>
       <c r="F177" s="29" t="n"/>
     </row>
     <row r="178" s="160">
+      <c r="B178" t="n"/>
       <c r="E178" s="50" t="inlineStr">
         <is>
           <t>(3) 表示処理</t>
@@ -11352,6 +16082,7 @@
       <c r="AL178" s="126" t="n"/>
     </row>
     <row r="179">
+      <c r="B179" t="n"/>
       <c r="E179" s="64" t="n"/>
       <c r="F179" s="159" t="inlineStr">
         <is>
@@ -11390,6 +16121,9 @@
       <c r="AJ179" s="96" t="n"/>
       <c r="AK179" s="96" t="n"/>
       <c r="AL179" s="96" t="n"/>
+    </row>
+    <row r="180">
+      <c r="B180" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="187">
@@ -11625,7 +16359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BF136"/>
+  <dimension ref="A1:BF179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="16" min="1" max="7"/>
@@ -11802,6 +16536,7 @@
       </c>
     </row>
     <row r="6" ht="12" customHeight="1" s="160">
+      <c r="B6" t="n"/>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>3.1. 画面レイアウト</t>
@@ -11812,77 +16547,115 @@
       <c r="B7" t="n"/>
       <c r="AJ7" s="140" t="n"/>
     </row>
-    <row r="8" ht="12" customHeight="1" s="160"/>
+    <row r="8" ht="12" customHeight="1" s="160">
+      <c r="B8" t="n"/>
+    </row>
     <row r="9" ht="12" customHeight="1" s="160">
       <c r="B9" t="n"/>
     </row>
-    <row r="10" ht="12" customHeight="1" s="160"/>
+    <row r="10" ht="12" customHeight="1" s="160">
+      <c r="B10" t="n"/>
+    </row>
     <row r="11" ht="12" customHeight="1" s="160">
       <c r="B11" t="n"/>
     </row>
-    <row r="12" ht="12" customHeight="1" s="160"/>
+    <row r="12" ht="12" customHeight="1" s="160">
+      <c r="B12" t="n"/>
+    </row>
     <row r="13" ht="12" customHeight="1" s="160">
       <c r="B13" t="n"/>
     </row>
-    <row r="14" ht="12" customHeight="1" s="160"/>
+    <row r="14" ht="12" customHeight="1" s="160">
+      <c r="B14" t="n"/>
+    </row>
     <row r="15" ht="12" customHeight="1" s="160">
       <c r="B15" t="n"/>
     </row>
-    <row r="16" ht="12" customHeight="1" s="160"/>
+    <row r="16" ht="12" customHeight="1" s="160">
+      <c r="B16" t="n"/>
+    </row>
     <row r="17" ht="12" customHeight="1" s="160">
       <c r="B17" t="n"/>
     </row>
-    <row r="18" ht="12" customHeight="1" s="160"/>
+    <row r="18" ht="12" customHeight="1" s="160">
+      <c r="B18" t="n"/>
+    </row>
     <row r="19" ht="12" customHeight="1" s="160">
       <c r="B19" t="n"/>
     </row>
-    <row r="20" ht="12" customHeight="1" s="160"/>
+    <row r="20" ht="12" customHeight="1" s="160">
+      <c r="B20" t="n"/>
+    </row>
     <row r="21" ht="12" customHeight="1" s="160">
       <c r="B21" t="n"/>
     </row>
-    <row r="22" ht="12" customHeight="1" s="160"/>
+    <row r="22" ht="12" customHeight="1" s="160">
+      <c r="B22" t="n"/>
+    </row>
     <row r="23" ht="12" customHeight="1" s="160">
       <c r="B23" t="n"/>
     </row>
-    <row r="24" ht="12" customHeight="1" s="160"/>
+    <row r="24" ht="12" customHeight="1" s="160">
+      <c r="B24" t="n"/>
+    </row>
     <row r="25" ht="12" customHeight="1" s="160">
       <c r="B25" t="n"/>
     </row>
-    <row r="26" ht="12" customHeight="1" s="160"/>
+    <row r="26" ht="12" customHeight="1" s="160">
+      <c r="B26" t="n"/>
+    </row>
     <row r="27" ht="12" customHeight="1" s="160">
       <c r="B27" t="n"/>
     </row>
-    <row r="28" ht="12" customHeight="1" s="160"/>
+    <row r="28" ht="12" customHeight="1" s="160">
+      <c r="B28" t="n"/>
+    </row>
     <row r="29" ht="12" customHeight="1" s="160">
       <c r="B29" t="n"/>
     </row>
-    <row r="30" ht="12" customHeight="1" s="160"/>
+    <row r="30" ht="12" customHeight="1" s="160">
+      <c r="B30" t="n"/>
+    </row>
     <row r="31" ht="12" customHeight="1" s="160">
       <c r="B31" t="n"/>
     </row>
-    <row r="32" ht="12" customHeight="1" s="160"/>
+    <row r="32" ht="12" customHeight="1" s="160">
+      <c r="B32" t="n"/>
+    </row>
     <row r="33" ht="12" customHeight="1" s="160">
       <c r="B33" t="n"/>
     </row>
-    <row r="34" ht="12" customHeight="1" s="160"/>
+    <row r="34" ht="12" customHeight="1" s="160">
+      <c r="B34" t="n"/>
+    </row>
     <row r="35" ht="12" customHeight="1" s="160">
       <c r="B35" t="n"/>
     </row>
-    <row r="36" ht="12" customHeight="1" s="160"/>
+    <row r="36" ht="12" customHeight="1" s="160">
+      <c r="B36" t="n"/>
+    </row>
     <row r="37" ht="12" customHeight="1" s="160">
       <c r="B37" t="n"/>
     </row>
-    <row r="38" ht="12" customHeight="1" s="160"/>
-    <row r="39" ht="12" customHeight="1" s="160"/>
+    <row r="38" ht="12" customHeight="1" s="160">
+      <c r="B38" t="n"/>
+    </row>
+    <row r="39" ht="12" customHeight="1" s="160">
+      <c r="B39" t="n"/>
+    </row>
     <row r="40" ht="12" customHeight="1" s="160">
+      <c r="B40" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>3.2. 一覧表示</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="12" customHeight="1" s="160"/>
+    <row r="41" ht="12" customHeight="1" s="160">
+      <c r="B41" t="n"/>
+    </row>
     <row r="42" ht="12" customHeight="1" s="160">
+      <c r="B42" t="n"/>
       <c r="D42" s="97" t="inlineStr">
         <is>
           <t>No.</t>
@@ -11931,6 +16704,7 @@
       <c r="AC42" s="459" t="n"/>
     </row>
     <row r="43" ht="12" customHeight="1" s="160">
+      <c r="B43" t="n"/>
       <c r="D43" s="124" t="n">
         <v>1</v>
       </c>
@@ -11976,8 +16750,11 @@
       <c r="AB43" s="460" t="n"/>
       <c r="AC43" s="461" t="n"/>
     </row>
-    <row r="44" ht="11.25" customHeight="1" s="160"/>
+    <row r="44" ht="11.25" customHeight="1" s="160">
+      <c r="B44" t="n"/>
+    </row>
     <row r="45">
+      <c r="B45" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>3.3. 画面項目定義</t>
@@ -12002,6 +16779,7 @@
       <c r="BA45" s="64" t="n"/>
     </row>
     <row r="46" customFormat="1" s="63">
+      <c r="B46" t="n"/>
       <c r="AJ46" s="92" t="n"/>
       <c r="AK46" s="92" t="n"/>
       <c r="AL46" s="92" t="n"/>
@@ -12021,6 +16799,7 @@
       <c r="AZ46" s="92" t="n"/>
     </row>
     <row r="47" customFormat="1" s="63">
+      <c r="B47" t="n"/>
       <c r="D47" s="141" t="n"/>
       <c r="AJ47" s="92" t="n"/>
       <c r="AK47" s="92" t="n"/>
@@ -12041,6 +16820,7 @@
       <c r="AZ47" s="92" t="n"/>
     </row>
     <row r="48" customFormat="1" s="63">
+      <c r="B48" t="n"/>
       <c r="D48" s="239" t="inlineStr">
         <is>
           <t>No.</t>
@@ -12096,6 +16876,7 @@
       <c r="AN48" s="92" t="n"/>
     </row>
     <row r="49" ht="11.25" customFormat="1" customHeight="1" s="63">
+      <c r="B49" t="n"/>
       <c r="D49" s="462" t="n"/>
       <c r="E49" s="239" t="inlineStr">
         <is>
@@ -12163,6 +16944,7 @@
       <c r="AT49" s="92" t="n"/>
     </row>
     <row r="50" customFormat="1" s="63">
+      <c r="B50" t="n"/>
       <c r="D50" s="465" t="n"/>
       <c r="E50" s="435" t="n"/>
       <c r="F50" s="436" t="n"/>
@@ -12213,6 +16995,7 @@
       <c r="AT50" s="92" t="n"/>
     </row>
     <row r="51" customFormat="1" s="63">
+      <c r="B51" t="n"/>
       <c r="D51" s="467" t="inlineStr">
         <is>
           <t>領域名：プロジェクト情報入力</t>
@@ -12266,6 +17049,7 @@
       <c r="AT51" s="92" t="n"/>
     </row>
     <row r="52" ht="73.5" customFormat="1" customHeight="1" s="64">
+      <c r="B52" t="n"/>
       <c r="D52" s="158" t="n">
         <v>1</v>
       </c>
@@ -12338,6 +17122,7 @@
       <c r="AP52" s="366" t="n"/>
     </row>
     <row r="53" ht="73.5" customFormat="1" customHeight="1" s="64">
+      <c r="B53" t="n"/>
       <c r="D53" s="158" t="n">
         <v>2</v>
       </c>
@@ -12410,6 +17195,7 @@
       <c r="AP53" s="366" t="n"/>
     </row>
     <row r="54" customFormat="1" s="63">
+      <c r="B54" t="n"/>
       <c r="D54" s="158" t="n">
         <v>3</v>
       </c>
@@ -12489,6 +17275,7 @@
       <c r="AT54" s="92" t="n"/>
     </row>
     <row r="55" ht="29.25" customFormat="1" customHeight="1" s="63">
+      <c r="B55" t="n"/>
       <c r="D55" s="158" t="n">
         <v>4</v>
       </c>
@@ -12568,6 +17355,7 @@
       <c r="AT55" s="92" t="n"/>
     </row>
     <row r="56" ht="29.25" customFormat="1" customHeight="1" s="63">
+      <c r="B56" t="n"/>
       <c r="D56" s="158" t="n">
         <v>5</v>
       </c>
@@ -12647,6 +17435,7 @@
       <c r="AT56" s="92" t="n"/>
     </row>
     <row r="57" ht="52.5" customHeight="1" s="160">
+      <c r="B57" t="n"/>
       <c r="D57" s="158" t="n">
         <v>6</v>
       </c>
@@ -12720,6 +17509,7 @@
       <c r="AP57" s="366" t="n"/>
     </row>
     <row r="58" ht="47.25" customFormat="1" customHeight="1" s="64">
+      <c r="B58" t="n"/>
       <c r="D58" s="158" t="n">
         <v>7</v>
       </c>
@@ -12791,6 +17581,7 @@
       <c r="AP58" s="366" t="n"/>
     </row>
     <row r="59" customFormat="1" s="64">
+      <c r="B59" t="n"/>
       <c r="D59" s="158" t="n">
         <v>8</v>
       </c>
@@ -12863,6 +17654,7 @@
       <c r="AV59" s="75" t="n"/>
     </row>
     <row r="60" customFormat="1" s="64">
+      <c r="B60" t="n"/>
       <c r="D60" s="158" t="n">
         <v>9</v>
       </c>
@@ -12936,6 +17728,7 @@
       <c r="AS60" s="92" t="n"/>
     </row>
     <row r="61" ht="22.5" customFormat="1" customHeight="1" s="63">
+      <c r="B61" t="n"/>
       <c r="D61" s="158" t="n">
         <v>10</v>
       </c>
@@ -13014,6 +17807,7 @@
       <c r="AR61" s="92" t="n"/>
     </row>
     <row r="62" ht="22.5" customFormat="1" customHeight="1" s="64">
+      <c r="B62" t="n"/>
       <c r="D62" s="158" t="n">
         <v>11</v>
       </c>
@@ -13086,6 +17880,7 @@
       <c r="AP62" s="366" t="n"/>
     </row>
     <row r="63" ht="28.5" customHeight="1" s="160">
+      <c r="B63" t="n"/>
       <c r="D63" s="158" t="n">
         <v>12</v>
       </c>
@@ -13157,6 +17952,7 @@
       <c r="AP63" s="366" t="n"/>
     </row>
     <row r="64" ht="73.5" customFormat="1" customHeight="1" s="64">
+      <c r="B64" t="n"/>
       <c r="D64" s="158" t="n">
         <v>13</v>
       </c>
@@ -13228,6 +18024,7 @@
       <c r="AP64" s="366" t="n"/>
     </row>
     <row r="65" ht="73.5" customFormat="1" customHeight="1" s="64">
+      <c r="B65" t="n"/>
       <c r="D65" s="158" t="n">
         <v>14</v>
       </c>
@@ -13299,6 +18096,7 @@
       <c r="AP65" s="366" t="n"/>
     </row>
     <row r="66" ht="11.25" customFormat="1" customHeight="1" s="63">
+      <c r="B66" t="n"/>
       <c r="D66" s="158" t="n">
         <v>15</v>
       </c>
@@ -13378,6 +18176,7 @@
       <c r="AT66" s="92" t="n"/>
     </row>
     <row r="67" ht="29.25" customFormat="1" customHeight="1" s="63">
+      <c r="B67" t="n"/>
       <c r="D67" s="158" t="n">
         <v>16</v>
       </c>
@@ -13457,6 +18256,7 @@
       <c r="AT67" s="92" t="n"/>
     </row>
     <row r="68" ht="29.25" customFormat="1" customHeight="1" s="63">
+      <c r="B68" t="n"/>
       <c r="D68" s="158" t="n">
         <v>17</v>
       </c>
@@ -13536,6 +18336,7 @@
       <c r="AT68" s="92" t="n"/>
     </row>
     <row r="69" ht="52.5" customHeight="1" s="160">
+      <c r="B69" t="n"/>
       <c r="D69" s="158" t="n">
         <v>18</v>
       </c>
@@ -13607,6 +18408,7 @@
       <c r="AP69" s="366" t="n"/>
     </row>
     <row r="70" ht="47.25" customFormat="1" customHeight="1" s="64">
+      <c r="B70" t="n"/>
       <c r="D70" s="158" t="n">
         <v>19</v>
       </c>
@@ -13678,6 +18480,7 @@
       <c r="AP70" s="366" t="n"/>
     </row>
     <row r="71" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B71" t="n"/>
       <c r="D71" s="158" t="n">
         <v>20</v>
       </c>
@@ -13750,6 +18553,7 @@
       <c r="AV71" s="75" t="n"/>
     </row>
     <row r="72" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B72" t="n"/>
       <c r="D72" s="158" t="n">
         <v>21</v>
       </c>
@@ -13823,6 +18627,7 @@
       <c r="AS72" s="92" t="n"/>
     </row>
     <row r="73" ht="22.5" customFormat="1" customHeight="1" s="63">
+      <c r="B73" t="n"/>
       <c r="D73" s="158" t="n">
         <v>22</v>
       </c>
@@ -13900,6 +18705,7 @@
       <c r="AR73" s="92" t="n"/>
     </row>
     <row r="74" ht="22.5" customFormat="1" customHeight="1" s="64">
+      <c r="B74" t="n"/>
       <c r="D74" s="158" t="n">
         <v>23</v>
       </c>
@@ -13971,6 +18777,7 @@
       <c r="AP74" s="366" t="n"/>
     </row>
     <row r="75" ht="28.5" customHeight="1" s="160">
+      <c r="B75" t="n"/>
       <c r="D75" s="158" t="n">
         <v>24</v>
       </c>
@@ -14042,6 +18849,7 @@
       <c r="AP75" s="366" t="n"/>
     </row>
     <row r="76" customFormat="1" s="63">
+      <c r="B76" t="n"/>
       <c r="AJ76" s="92" t="n"/>
       <c r="AK76" s="92" t="n"/>
       <c r="AL76" s="92" t="n"/>
@@ -14061,6 +18869,7 @@
       <c r="AZ76" s="92" t="n"/>
     </row>
     <row r="77">
+      <c r="B77" t="n"/>
       <c r="D77" s="64" t="n"/>
       <c r="E77" s="96" t="n"/>
       <c r="F77" s="96" t="n"/>
@@ -14096,6 +18905,7 @@
       <c r="AJ77" s="96" t="n"/>
     </row>
     <row r="78">
+      <c r="B78" t="n"/>
       <c r="C78" s="16" t="inlineStr">
         <is>
           <t>3.4. 入出力一覧</t>
@@ -14136,10 +18946,12 @@
       <c r="AJ78" s="96" t="n"/>
     </row>
     <row r="79" ht="11.25" customHeight="1" s="160">
+      <c r="B79" t="n"/>
       <c r="AI79" s="96" t="n"/>
       <c r="AJ79" s="96" t="n"/>
     </row>
     <row r="80">
+      <c r="B80" t="n"/>
       <c r="D80" s="469" t="inlineStr">
         <is>
           <t>No.</t>
@@ -14197,6 +19009,7 @@
       <c r="AH80" s="428" t="n"/>
     </row>
     <row r="81">
+      <c r="B81" t="n"/>
       <c r="D81" s="465" t="n"/>
       <c r="E81" s="435" t="n"/>
       <c r="F81" s="436" t="n"/>
@@ -14250,6 +19063,7 @@
       <c r="AH81" s="437" t="n"/>
     </row>
     <row r="82" ht="11.25" customHeight="1" s="160">
+      <c r="B82" t="n"/>
       <c r="D82" s="111" t="n">
         <v>1</v>
       </c>
@@ -14321,6 +19135,7 @@
       <c r="AH82" s="366" t="n"/>
     </row>
     <row r="83">
+      <c r="B83" t="n"/>
       <c r="D83" s="111" t="n">
         <v>2</v>
       </c>
@@ -14392,6 +19207,7 @@
       <c r="AH83" s="366" t="n"/>
     </row>
     <row r="84">
+      <c r="B84" t="n"/>
       <c r="D84" s="101" t="n"/>
       <c r="E84" s="104" t="n"/>
       <c r="F84" s="104" t="n"/>
@@ -14425,6 +19241,7 @@
       <c r="AH84" s="104" t="n"/>
     </row>
     <row r="85">
+      <c r="B85" t="n"/>
       <c r="D85" s="64" t="n"/>
       <c r="E85" s="96" t="n"/>
       <c r="F85" s="96" t="n"/>
@@ -14460,14 +19277,18 @@
       <c r="AJ85" s="96" t="n"/>
     </row>
     <row r="86">
+      <c r="B86" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>3.5. 画面イベント一覧</t>
         </is>
       </c>
     </row>
-    <row r="87"/>
+    <row r="87">
+      <c r="B87" t="n"/>
+    </row>
     <row r="88" ht="11.25" customHeight="1" s="160">
+      <c r="B88" t="n"/>
       <c r="C88" s="75" t="n"/>
       <c r="D88" s="113" t="inlineStr">
         <is>
@@ -14526,6 +19347,7 @@
       <c r="AH88" s="459" t="n"/>
     </row>
     <row r="89" ht="23.25" customHeight="1" s="160">
+      <c r="B89" t="n"/>
       <c r="D89" s="106" t="n">
         <v>1</v>
       </c>
@@ -14581,6 +19403,7 @@
       <c r="AH89" s="461" t="n"/>
     </row>
     <row r="90" ht="24" customHeight="1" s="160">
+      <c r="B90" t="n"/>
       <c r="D90" s="106" t="n">
         <v>2</v>
       </c>
@@ -14636,6 +19459,7 @@
       <c r="AH90" s="461" t="n"/>
     </row>
     <row r="91">
+      <c r="B91" t="n"/>
       <c r="D91" s="95" t="n"/>
       <c r="E91" s="104" t="n"/>
       <c r="F91" s="104" t="n"/>
@@ -14669,6 +19493,7 @@
       <c r="AH91" s="104" t="n"/>
     </row>
     <row r="92">
+      <c r="B92" t="n"/>
       <c r="D92" s="95" t="n"/>
       <c r="E92" s="104" t="n"/>
       <c r="F92" s="104" t="n"/>
@@ -14702,6 +19527,7 @@
       <c r="AH92" s="104" t="n"/>
     </row>
     <row r="93">
+      <c r="B93" t="n"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>3.6. 画面イベント詳細</t>
@@ -14709,6 +19535,7 @@
       </c>
     </row>
     <row r="94">
+      <c r="B94" t="n"/>
       <c r="E94" s="92" t="n"/>
       <c r="F94" s="93" t="n"/>
       <c r="G94" s="159" t="n"/>
@@ -14737,6 +19564,7 @@
       <c r="BF94" s="77" t="n"/>
     </row>
     <row r="95" s="160">
+      <c r="B95" t="n"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>3.6.1. 登録イベント</t>
@@ -14744,6 +19572,7 @@
       </c>
     </row>
     <row r="96" s="160">
+      <c r="B96" t="n"/>
       <c r="E96" s="26" t="inlineStr">
         <is>
           <t>(1) バリデーション処理</t>
@@ -14752,10 +19581,12 @@
       <c r="F96" s="26" t="n"/>
     </row>
     <row r="97" s="160">
+      <c r="B97" t="n"/>
       <c r="E97" s="26" t="n"/>
       <c r="F97" s="26" t="n"/>
     </row>
     <row r="98" s="160">
+      <c r="B98" t="n"/>
       <c r="E98" s="26" t="n"/>
       <c r="F98" s="26" t="inlineStr">
         <is>
@@ -14763,8 +19594,11 @@
         </is>
       </c>
     </row>
-    <row r="99" s="160"/>
+    <row r="99" s="160">
+      <c r="B99" t="n"/>
+    </row>
     <row r="100" s="160">
+      <c r="B100" t="n"/>
       <c r="E100" s="26" t="n"/>
       <c r="F100" t="inlineStr">
         <is>
@@ -14773,36 +19607,51 @@
       </c>
     </row>
     <row r="101">
+      <c r="B101" t="n"/>
       <c r="E101" s="29" t="n"/>
       <c r="F101" s="29" t="n"/>
     </row>
-    <row r="102"/>
-    <row r="103"/>
+    <row r="102">
+      <c r="B102" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" t="n"/>
+    </row>
     <row r="104">
+      <c r="B104" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>(2) DBアクセス（登録、更新処理）</t>
         </is>
       </c>
     </row>
-    <row r="105"/>
+    <row r="105">
+      <c r="B105" t="n"/>
+    </row>
     <row r="106">
+      <c r="B106" t="n"/>
       <c r="F106" t="inlineStr">
         <is>
           <t>表示内容をデータベースに登録する。登録仕様については下記の通り。</t>
         </is>
       </c>
     </row>
-    <row r="107"/>
+    <row r="107">
+      <c r="B107" t="n"/>
+    </row>
     <row r="108">
+      <c r="B108" t="n"/>
       <c r="F108" t="inlineStr">
         <is>
           <t>プロジェクトテーブル</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="12" customHeight="1" s="160"/>
+    <row r="109" ht="12" customHeight="1" s="160">
+      <c r="B109" t="n"/>
+    </row>
     <row r="110" ht="12" customHeight="1" s="160">
+      <c r="B110" t="n"/>
       <c r="G110" s="239" t="inlineStr">
         <is>
           <t>No.</t>
@@ -14853,6 +19702,7 @@
       <c r="AH110" s="428" t="n"/>
     </row>
     <row r="111" ht="12" customHeight="1" s="160">
+      <c r="B111" t="n"/>
       <c r="G111" s="465" t="n"/>
       <c r="H111" s="435" t="n"/>
       <c r="I111" s="436" t="n"/>
@@ -14891,6 +19741,7 @@
       <c r="AH111" s="437" t="n"/>
     </row>
     <row r="112" ht="12" customHeight="1" s="160">
+      <c r="B112" t="n"/>
       <c r="G112" s="106" t="n">
         <v>1</v>
       </c>
@@ -14939,6 +19790,7 @@
       <c r="AH112" s="366" t="n"/>
     </row>
     <row r="113" ht="12" customHeight="1" s="160">
+      <c r="B113" t="n"/>
       <c r="G113" s="106" t="n">
         <v>2</v>
       </c>
@@ -14987,6 +19839,7 @@
       <c r="AH113" s="366" t="n"/>
     </row>
     <row r="114" ht="12" customHeight="1" s="160">
+      <c r="B114" t="n"/>
       <c r="G114" s="106" t="n">
         <v>3</v>
       </c>
@@ -15028,6 +19881,7 @@
       <c r="AH114" s="366" t="n"/>
     </row>
     <row r="115" ht="12.75" customHeight="1" s="160">
+      <c r="B115" t="n"/>
       <c r="G115" s="106" t="n">
         <v>4</v>
       </c>
@@ -15069,6 +19923,7 @@
       <c r="AH115" s="366" t="n"/>
     </row>
     <row r="116" ht="12" customHeight="1" s="160">
+      <c r="B116" t="n"/>
       <c r="G116" s="106" t="n">
         <v>5</v>
       </c>
@@ -15110,6 +19965,7 @@
       <c r="AH116" s="366" t="n"/>
     </row>
     <row r="117" ht="12" customHeight="1" s="160">
+      <c r="B117" t="n"/>
       <c r="G117" s="106" t="n">
         <v>6</v>
       </c>
@@ -15151,6 +20007,7 @@
       <c r="AH117" s="366" t="n"/>
     </row>
     <row r="118" ht="12" customHeight="1" s="160">
+      <c r="B118" t="n"/>
       <c r="G118" s="106" t="n">
         <v>7</v>
       </c>
@@ -15192,6 +20049,7 @@
       <c r="AH118" s="366" t="n"/>
     </row>
     <row r="119" ht="12" customHeight="1" s="160">
+      <c r="B119" t="n"/>
       <c r="G119" s="106" t="n">
         <v>8</v>
       </c>
@@ -15233,6 +20091,7 @@
       <c r="AH119" s="366" t="n"/>
     </row>
     <row r="120" ht="39.95" customHeight="1" s="160">
+      <c r="B120" t="n"/>
       <c r="G120" s="106" t="n">
         <v>9</v>
       </c>
@@ -15274,6 +20133,7 @@
       <c r="AH120" s="366" t="n"/>
     </row>
     <row r="121" ht="12" customHeight="1" s="160">
+      <c r="B121" t="n"/>
       <c r="G121" s="106" t="n">
         <v>10</v>
       </c>
@@ -15315,6 +20175,7 @@
       <c r="AH121" s="366" t="n"/>
     </row>
     <row r="122" ht="12" customHeight="1" s="160">
+      <c r="B122" t="n"/>
       <c r="G122" s="106" t="n">
         <v>11</v>
       </c>
@@ -15356,6 +20217,7 @@
       <c r="AH122" s="366" t="n"/>
     </row>
     <row r="123" ht="12" customHeight="1" s="160">
+      <c r="B123" t="n"/>
       <c r="G123" s="106" t="n">
         <v>12</v>
       </c>
@@ -15400,6 +20262,7 @@
       <c r="AH123" s="366" t="n"/>
     </row>
     <row r="124" ht="12" customHeight="1" s="160">
+      <c r="B124" t="n"/>
       <c r="G124" s="106" t="n">
         <v>13</v>
       </c>
@@ -15447,47 +20310,195 @@
       <c r="AG124" s="365" t="n"/>
       <c r="AH124" s="366" t="n"/>
     </row>
-    <row r="125" ht="12" customHeight="1" s="160"/>
-    <row r="126"/>
+    <row r="125" ht="12" customHeight="1" s="160">
+      <c r="B125" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" t="n"/>
+    </row>
     <row r="127">
+      <c r="B127" t="n"/>
       <c r="E127" s="16" t="inlineStr">
         <is>
           <t>(3) 表示処理</t>
         </is>
       </c>
     </row>
-    <row r="128"/>
+    <row r="128">
+      <c r="B128" t="n"/>
+    </row>
     <row r="129">
+      <c r="B129" t="n"/>
       <c r="F129" t="inlineStr">
         <is>
           <t>プロジェクト登録完了画面を表示する。画面レイアウト、表示項目については「4. プロジェクト登録完了画面」を参照。</t>
         </is>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131"/>
+    <row r="130">
+      <c r="B130" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" t="n"/>
+    </row>
     <row r="132">
+      <c r="B132" t="n"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>3.6.2. 戻るイベント</t>
         </is>
       </c>
     </row>
-    <row r="133"/>
+    <row r="133">
+      <c r="B133" t="n"/>
+    </row>
     <row r="134">
+      <c r="B134" t="n"/>
       <c r="E134" s="16" t="inlineStr">
         <is>
           <t>(1) 表示処理</t>
         </is>
       </c>
     </row>
-    <row r="135"/>
+    <row r="135">
+      <c r="B135" t="n"/>
+    </row>
     <row r="136">
+      <c r="B136" t="n"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>当画面に表示していた内容をプロジェクト登録画面に表示する。画面レイアウト、表示項目については「2. プロジェクト登録画面」を参照。</t>
         </is>
       </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="294">
@@ -15829,7 +20840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BA72"/>
+  <dimension ref="A1:BA179"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="4.83203125" defaultRowHeight="11.25"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="16" min="1" max="7"/>
@@ -16008,42 +21019,97 @@
       </c>
     </row>
     <row r="6" ht="12" customHeight="1" s="160">
+      <c r="B6" t="n"/>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>4.1. 画面レイアウト</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="12" customHeight="1" s="160"/>
+    <row r="7" ht="12" customHeight="1" s="160">
+      <c r="B7" t="n"/>
+    </row>
     <row r="8" ht="12" customHeight="1" s="160">
+      <c r="B8" t="n"/>
       <c r="AK8" s="140" t="n"/>
     </row>
-    <row r="9" ht="12" customHeight="1" s="160"/>
-    <row r="10" ht="12" customHeight="1" s="160"/>
-    <row r="11" ht="12" customHeight="1" s="160"/>
-    <row r="12" ht="12" customHeight="1" s="160"/>
-    <row r="13" ht="12" customHeight="1" s="160"/>
-    <row r="14" ht="12" customHeight="1" s="160"/>
-    <row r="15" ht="12" customHeight="1" s="160"/>
-    <row r="16" ht="12" customHeight="1" s="160"/>
-    <row r="17" ht="12" customHeight="1" s="160"/>
-    <row r="18" ht="12" customHeight="1" s="160"/>
-    <row r="19" ht="12" customHeight="1" s="160"/>
-    <row r="20" ht="12" customHeight="1" s="160"/>
-    <row r="21" ht="12" customHeight="1" s="160"/>
-    <row r="22" ht="12" customHeight="1" s="160"/>
-    <row r="23" ht="12" customHeight="1" s="160"/>
-    <row r="24" ht="12" customHeight="1" s="160"/>
-    <row r="25" ht="12" customHeight="1" s="160"/>
-    <row r="26" ht="12" customHeight="1" s="160"/>
-    <row r="27" ht="12" customHeight="1" s="160"/>
-    <row r="28" ht="12" customHeight="1" s="160"/>
-    <row r="29" ht="12" customHeight="1" s="160"/>
-    <row r="30" ht="12" customHeight="1" s="160"/>
-    <row r="31" ht="12" customHeight="1" s="160"/>
-    <row r="32" ht="12" customHeight="1" s="160"/>
-    <row r="33" ht="12" customHeight="1" s="160"/>
+    <row r="9" ht="12" customHeight="1" s="160">
+      <c r="B9" t="n"/>
+    </row>
+    <row r="10" ht="12" customHeight="1" s="160">
+      <c r="B10" t="n"/>
+    </row>
+    <row r="11" ht="12" customHeight="1" s="160">
+      <c r="B11" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1" s="160">
+      <c r="B12" t="n"/>
+    </row>
+    <row r="13" ht="12" customHeight="1" s="160">
+      <c r="B13" t="n"/>
+    </row>
+    <row r="14" ht="12" customHeight="1" s="160">
+      <c r="B14" t="n"/>
+    </row>
+    <row r="15" ht="12" customHeight="1" s="160">
+      <c r="B15" t="n"/>
+    </row>
+    <row r="16" ht="12" customHeight="1" s="160">
+      <c r="B16" t="n"/>
+    </row>
+    <row r="17" ht="12" customHeight="1" s="160">
+      <c r="B17" t="n"/>
+    </row>
+    <row r="18" ht="12" customHeight="1" s="160">
+      <c r="B18" t="n"/>
+    </row>
+    <row r="19" ht="12" customHeight="1" s="160">
+      <c r="B19" t="n"/>
+    </row>
+    <row r="20" ht="12" customHeight="1" s="160">
+      <c r="B20" t="n"/>
+    </row>
+    <row r="21" ht="12" customHeight="1" s="160">
+      <c r="B21" t="n"/>
+    </row>
+    <row r="22" ht="12" customHeight="1" s="160">
+      <c r="B22" t="n"/>
+    </row>
+    <row r="23" ht="12" customHeight="1" s="160">
+      <c r="B23" t="n"/>
+    </row>
+    <row r="24" ht="12" customHeight="1" s="160">
+      <c r="B24" t="n"/>
+    </row>
+    <row r="25" ht="12" customHeight="1" s="160">
+      <c r="B25" t="n"/>
+    </row>
+    <row r="26" ht="12" customHeight="1" s="160">
+      <c r="B26" t="n"/>
+    </row>
+    <row r="27" ht="12" customHeight="1" s="160">
+      <c r="B27" t="n"/>
+    </row>
+    <row r="28" ht="12" customHeight="1" s="160">
+      <c r="B28" t="n"/>
+    </row>
+    <row r="29" ht="12" customHeight="1" s="160">
+      <c r="B29" t="n"/>
+    </row>
+    <row r="30" ht="12" customHeight="1" s="160">
+      <c r="B30" t="n"/>
+    </row>
+    <row r="31" ht="12" customHeight="1" s="160">
+      <c r="B31" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1" s="160">
+      <c r="B32" t="n"/>
+    </row>
+    <row r="33" ht="12" customHeight="1" s="160">
+      <c r="B33" t="n"/>
+    </row>
     <row r="34" ht="12" customHeight="1" s="160">
+      <c r="B34" t="n"/>
       <c r="D34" s="103" t="n"/>
       <c r="E34" s="103" t="n"/>
       <c r="F34" s="103" t="n"/>
@@ -16077,6 +21143,7 @@
       <c r="AH34" s="103" t="n"/>
     </row>
     <row r="35">
+      <c r="B35" t="n"/>
       <c r="C35" s="26" t="inlineStr">
         <is>
           <t>4.2. 一覧表示</t>
@@ -16114,6 +21181,7 @@
       <c r="AH35" s="103" t="n"/>
     </row>
     <row r="36">
+      <c r="B36" t="n"/>
       <c r="C36" s="29" t="n"/>
       <c r="D36" s="103" t="n"/>
       <c r="E36" s="103" t="n"/>
@@ -16147,6 +21215,7 @@
       <c r="AH36" s="103" t="n"/>
     </row>
     <row r="37">
+      <c r="B37" t="n"/>
       <c r="D37" s="97" t="inlineStr">
         <is>
           <t>No.</t>
@@ -16200,6 +21269,7 @@
       <c r="AH37" s="103" t="n"/>
     </row>
     <row r="38" ht="11.25" customHeight="1" s="160">
+      <c r="B38" t="n"/>
       <c r="D38" s="124" t="n">
         <v>1</v>
       </c>
@@ -16243,6 +21313,7 @@
       <c r="AM38" s="29" t="n"/>
     </row>
     <row r="39" ht="11.25" customHeight="1" s="160">
+      <c r="B39" t="n"/>
       <c r="D39" s="103" t="n"/>
       <c r="E39" s="103" t="n"/>
       <c r="F39" s="103" t="n"/>
@@ -16271,8 +21342,11 @@
       <c r="AC39" s="103" t="n"/>
       <c r="AM39" s="29" t="n"/>
     </row>
-    <row r="40" ht="11.25" customHeight="1" s="160"/>
+    <row r="40" ht="11.25" customHeight="1" s="160">
+      <c r="B40" t="n"/>
+    </row>
     <row r="41">
+      <c r="B41" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>4.3. 画面項目定義</t>
@@ -16297,6 +21371,7 @@
       <c r="BA41" s="64" t="n"/>
     </row>
     <row r="42" customFormat="1" s="63">
+      <c r="B42" t="n"/>
       <c r="AC42" s="92" t="n"/>
       <c r="AD42" s="92" t="n"/>
       <c r="AE42" s="92" t="n"/>
@@ -16313,6 +21388,7 @@
       <c r="AP42" s="92" t="n"/>
     </row>
     <row r="43" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B43" t="n"/>
       <c r="D43" s="496" t="inlineStr">
         <is>
           <t>No.</t>
@@ -16361,6 +21437,7 @@
       <c r="AL43" s="92" t="n"/>
     </row>
     <row r="44" ht="11.25" customFormat="1" customHeight="1" s="64">
+      <c r="B44" t="n"/>
       <c r="D44" s="462" t="n"/>
       <c r="E44" s="239" t="inlineStr">
         <is>
@@ -16419,6 +21496,7 @@
       <c r="AL44" s="92" t="n"/>
     </row>
     <row r="45" customFormat="1" s="64">
+      <c r="B45" t="n"/>
       <c r="D45" s="465" t="n"/>
       <c r="E45" s="435" t="n"/>
       <c r="F45" s="436" t="n"/>
@@ -16455,6 +21533,7 @@
       <c r="AL45" s="92" t="n"/>
     </row>
     <row r="46" ht="12" customHeight="1" s="160">
+      <c r="B46" t="n"/>
       <c r="D46" s="106" t="n">
         <v>1</v>
       </c>
@@ -16518,6 +21597,7 @@
       <c r="AH46" s="103" t="n"/>
     </row>
     <row r="47" ht="11.25" customHeight="1" s="160">
+      <c r="B47" t="n"/>
       <c r="D47" s="95" t="n"/>
       <c r="E47" s="75" t="n"/>
       <c r="F47" s="75" t="n"/>
@@ -16555,6 +21635,7 @@
       <c r="AM47" s="117" t="n"/>
     </row>
     <row r="48">
+      <c r="B48" t="n"/>
       <c r="D48" s="64" t="n"/>
       <c r="E48" s="96" t="n"/>
       <c r="F48" s="96" t="n"/>
@@ -16590,6 +21671,7 @@
       <c r="AJ48" s="96" t="n"/>
     </row>
     <row r="49">
+      <c r="B49" t="n"/>
       <c r="C49" s="16" t="inlineStr">
         <is>
           <t>4.4. 入出力一覧</t>
@@ -16630,10 +21712,12 @@
       <c r="AJ49" s="96" t="n"/>
     </row>
     <row r="50" ht="11.25" customHeight="1" s="160">
+      <c r="B50" t="n"/>
       <c r="AI50" s="96" t="n"/>
       <c r="AJ50" s="96" t="n"/>
     </row>
     <row r="51">
+      <c r="B51" t="n"/>
       <c r="D51" s="469" t="inlineStr">
         <is>
           <t>No.</t>
@@ -16691,6 +21775,7 @@
       <c r="AH51" s="428" t="n"/>
     </row>
     <row r="52">
+      <c r="B52" t="n"/>
       <c r="D52" s="465" t="n"/>
       <c r="E52" s="435" t="n"/>
       <c r="F52" s="436" t="n"/>
@@ -16744,6 +21829,7 @@
       <c r="AH52" s="437" t="n"/>
     </row>
     <row r="53">
+      <c r="B53" t="n"/>
       <c r="D53" s="111" t="n">
         <v>1</v>
       </c>
@@ -16811,6 +21897,7 @@
       <c r="AH53" s="366" t="n"/>
     </row>
     <row r="54">
+      <c r="B54" t="n"/>
       <c r="D54" s="104" t="n"/>
       <c r="E54" s="104" t="n"/>
       <c r="F54" s="104" t="n"/>
@@ -16844,6 +21931,7 @@
       <c r="AH54" s="104" t="n"/>
     </row>
     <row r="55">
+      <c r="B55" t="n"/>
       <c r="D55" s="318" t="n"/>
       <c r="E55" s="318" t="n"/>
       <c r="F55" s="318" t="n"/>
@@ -16877,13 +21965,18 @@
       <c r="AH55" s="318" t="n"/>
     </row>
     <row r="56">
+      <c r="B56" t="n"/>
       <c r="C56" s="16" t="inlineStr">
         <is>
           <t>4.5. 画面イベント一覧</t>
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="B57" t="n"/>
+    </row>
     <row r="58" ht="15" customHeight="1" s="160">
+      <c r="B58" t="n"/>
       <c r="D58" s="239" t="inlineStr">
         <is>
           <t>No.</t>
@@ -16941,6 +22034,7 @@
       <c r="AH58" s="459" t="n"/>
     </row>
     <row r="59" ht="24.95" customHeight="1" s="160">
+      <c r="B59" t="n"/>
       <c r="D59" s="116" t="n">
         <v>1</v>
       </c>
@@ -16996,12 +22090,17 @@
       <c r="AH59" s="461" t="n"/>
     </row>
     <row r="60">
+      <c r="B60" t="n"/>
       <c r="AE60" s="413" t="n"/>
       <c r="AF60" s="498" t="n"/>
       <c r="AG60" s="498" t="n"/>
       <c r="AH60" s="498" t="n"/>
     </row>
+    <row r="61">
+      <c r="B61" t="n"/>
+    </row>
     <row r="62">
+      <c r="B62" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>4.6. 画面イベント詳細</t>
@@ -17009,30 +22108,369 @@
       </c>
     </row>
     <row r="63">
+      <c r="B63" t="n"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>4.6.1 登録開始イベント</t>
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="B64" t="n"/>
+    </row>
     <row r="65">
+      <c r="B65" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>プロジェクト登録画面へ遷移する。</t>
         </is>
       </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="n"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="n"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="n"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="94" t="n"/>
+      <c r="B70" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="94" t="n"/>
+      <c r="B71" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="94" t="n"/>
-    </row>
-    <row r="74" ht="11.25" customHeight="1" s="160"/>
-    <row r="76" ht="11.25" customHeight="1" s="160"/>
+      <c r="B72" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" t="n"/>
+    </row>
+    <row r="74" ht="11.25" customHeight="1" s="160">
+      <c r="B74" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" t="n"/>
+    </row>
+    <row r="76" ht="11.25" customHeight="1" s="160">
+      <c r="B76" t="n"/>
+    </row>
+    <row r="77">
+      <c r="B77" t="n"/>
+    </row>
+    <row r="78">
+      <c r="B78" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" t="n"/>
+    </row>
+    <row r="80">
+      <c r="B80" t="n"/>
+    </row>
+    <row r="81">
+      <c r="B81" t="n"/>
+    </row>
+    <row r="82">
+      <c r="B82" t="n"/>
+    </row>
+    <row r="83">
+      <c r="B83" t="n"/>
+    </row>
+    <row r="84">
+      <c r="B84" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" t="n"/>
+    </row>
+    <row r="86">
+      <c r="B86" t="n"/>
+    </row>
+    <row r="87">
+      <c r="B87" t="n"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="n"/>
+    </row>
+    <row r="89">
+      <c r="B89" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" t="n"/>
+    </row>
+    <row r="91">
+      <c r="B91" t="n"/>
+    </row>
+    <row r="92">
+      <c r="B92" t="n"/>
+    </row>
+    <row r="93">
+      <c r="B93" t="n"/>
+    </row>
+    <row r="94">
+      <c r="B94" t="n"/>
+    </row>
+    <row r="95">
+      <c r="B95" t="n"/>
+    </row>
+    <row r="96">
+      <c r="B96" t="n"/>
+    </row>
+    <row r="97">
+      <c r="B97" t="n"/>
+    </row>
+    <row r="98">
+      <c r="B98" t="n"/>
+    </row>
+    <row r="99">
+      <c r="B99" t="n"/>
+    </row>
+    <row r="100">
+      <c r="B100" t="n"/>
+    </row>
+    <row r="101">
+      <c r="B101" t="n"/>
+    </row>
+    <row r="102">
+      <c r="B102" t="n"/>
+    </row>
+    <row r="103">
+      <c r="B103" t="n"/>
+    </row>
+    <row r="104">
+      <c r="B104" t="n"/>
+    </row>
+    <row r="105">
+      <c r="B105" t="n"/>
+    </row>
+    <row r="106">
+      <c r="B106" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" t="n"/>
+    </row>
+    <row r="109">
+      <c r="B109" t="n"/>
+    </row>
+    <row r="110">
+      <c r="B110" t="n"/>
+    </row>
+    <row r="111">
+      <c r="B111" t="n"/>
+    </row>
+    <row r="112">
+      <c r="B112" t="n"/>
+    </row>
+    <row r="113">
+      <c r="B113" t="n"/>
+    </row>
+    <row r="114">
+      <c r="B114" t="n"/>
+    </row>
+    <row r="115">
+      <c r="B115" t="n"/>
+    </row>
+    <row r="116">
+      <c r="B116" t="n"/>
+    </row>
+    <row r="117">
+      <c r="B117" t="n"/>
+    </row>
+    <row r="118">
+      <c r="B118" t="n"/>
+    </row>
+    <row r="119">
+      <c r="B119" t="n"/>
+    </row>
+    <row r="120">
+      <c r="B120" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" t="n"/>
+    </row>
+    <row r="126">
+      <c r="B126" t="n"/>
+    </row>
+    <row r="127">
+      <c r="B127" t="n"/>
+    </row>
+    <row r="128">
+      <c r="B128" t="n"/>
+    </row>
+    <row r="129">
+      <c r="B129" t="n"/>
+    </row>
+    <row r="130">
+      <c r="B130" t="n"/>
+    </row>
+    <row r="131">
+      <c r="B131" t="n"/>
+    </row>
+    <row r="132">
+      <c r="B132" t="n"/>
+    </row>
+    <row r="133">
+      <c r="B133" t="n"/>
+    </row>
+    <row r="134">
+      <c r="B134" t="n"/>
+    </row>
+    <row r="135">
+      <c r="B135" t="n"/>
+    </row>
+    <row r="136">
+      <c r="B136" t="n"/>
+    </row>
+    <row r="137">
+      <c r="B137" t="n"/>
+    </row>
+    <row r="138">
+      <c r="B138" t="n"/>
+    </row>
+    <row r="139">
+      <c r="B139" t="n"/>
+    </row>
+    <row r="140">
+      <c r="B140" t="n"/>
+    </row>
+    <row r="141">
+      <c r="B141" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" t="n"/>
+    </row>
+    <row r="144">
+      <c r="B144" t="n"/>
+    </row>
+    <row r="145">
+      <c r="B145" t="n"/>
+    </row>
+    <row r="146">
+      <c r="B146" t="n"/>
+    </row>
+    <row r="147">
+      <c r="B147" t="n"/>
+    </row>
+    <row r="148">
+      <c r="B148" t="n"/>
+    </row>
+    <row r="149">
+      <c r="B149" t="n"/>
+    </row>
+    <row r="150">
+      <c r="B150" t="n"/>
+    </row>
+    <row r="151">
+      <c r="B151" t="n"/>
+    </row>
+    <row r="152">
+      <c r="B152" t="n"/>
+    </row>
+    <row r="153">
+      <c r="B153" t="n"/>
+    </row>
+    <row r="154">
+      <c r="B154" t="n"/>
+    </row>
+    <row r="155">
+      <c r="B155" t="n"/>
+    </row>
+    <row r="156">
+      <c r="B156" t="n"/>
+    </row>
+    <row r="157">
+      <c r="B157" t="n"/>
+    </row>
+    <row r="158">
+      <c r="B158" t="n"/>
+    </row>
+    <row r="159">
+      <c r="B159" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" t="n"/>
+    </row>
+    <row r="161">
+      <c r="B161" t="n"/>
+    </row>
+    <row r="162">
+      <c r="B162" t="n"/>
+    </row>
+    <row r="163">
+      <c r="B163" t="n"/>
+    </row>
+    <row r="164">
+      <c r="B164" t="n"/>
+    </row>
+    <row r="165">
+      <c r="B165" t="n"/>
+    </row>
+    <row r="166">
+      <c r="B166" t="n"/>
+    </row>
+    <row r="167">
+      <c r="B167" t="n"/>
+    </row>
+    <row r="168">
+      <c r="B168" t="n"/>
+    </row>
+    <row r="169">
+      <c r="B169" t="n"/>
+    </row>
+    <row r="170">
+      <c r="B170" t="n"/>
+    </row>
+    <row r="171">
+      <c r="B171" t="n"/>
+    </row>
+    <row r="172">
+      <c r="B172" t="n"/>
+    </row>
+    <row r="173">
+      <c r="B173" t="n"/>
+    </row>
+    <row r="174">
+      <c r="B174" t="n"/>
+    </row>
+    <row r="175">
+      <c r="B175" t="n"/>
+    </row>
+    <row r="176">
+      <c r="B176" t="n"/>
+    </row>
+    <row r="177">
+      <c r="B177" t="n"/>
+    </row>
+    <row r="178">
+      <c r="B178" t="n"/>
+    </row>
+    <row r="179">
+      <c r="B179" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="60">
     <mergeCell ref="AG2:AI2"/>
@@ -17127,6 +22565,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="33" min="0" max="34" man="1"/>
   </rowBreaks>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
